--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1092,25 +1092,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="C16" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D16" t="n">
-        <v>55.9</v>
+        <v>57.4</v>
       </c>
       <c r="E16" t="n">
-        <v>186</v>
+        <v>209</v>
       </c>
       <c r="F16" t="n">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="G16" t="n">
-        <v>213</v>
+        <v>237</v>
       </c>
       <c r="H16" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="I16" t="n">
         <v>504</v>
@@ -1119,7 +1119,7 @@
         <v>18249</v>
       </c>
       <c r="K16" t="n">
-        <v>13168</v>
+        <v>13187</v>
       </c>
       <c r="L16" t="n">
         <v>303026</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1030,7 +1030,7 @@
         <v>5491</v>
       </c>
       <c r="J14" t="n">
-        <v>41110</v>
+        <v>41195</v>
       </c>
       <c r="K14" t="n">
         <v>12147</v>
@@ -1039,7 +1039,7 @@
         <v>293779</v>
       </c>
       <c r="M14" t="n">
-        <v>525968</v>
+        <v>526053</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>8743</v>
+        <v>8863</v>
       </c>
       <c r="J15" t="n">
-        <v>103332</v>
+        <v>104700</v>
       </c>
       <c r="K15" t="n">
         <v>12994</v>
       </c>
       <c r="L15" t="n">
-        <v>302522</v>
+        <v>302642</v>
       </c>
       <c r="M15" t="n">
-        <v>629300</v>
+        <v>630753</v>
       </c>
     </row>
     <row r="16">
@@ -1092,40 +1092,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>193</v>
+        <v>247</v>
       </c>
       <c r="C16" t="n">
-        <v>143</v>
+        <v>195</v>
       </c>
       <c r="D16" t="n">
-        <v>57.4</v>
+        <v>55.9</v>
       </c>
       <c r="E16" t="n">
-        <v>209</v>
+        <v>266</v>
       </c>
       <c r="F16" t="n">
-        <v>150</v>
+        <v>220</v>
       </c>
       <c r="G16" t="n">
-        <v>237</v>
+        <v>297</v>
       </c>
       <c r="H16" t="n">
-        <v>160</v>
+        <v>234</v>
       </c>
       <c r="I16" t="n">
         <v>504</v>
       </c>
       <c r="J16" t="n">
-        <v>18249</v>
+        <v>19777</v>
       </c>
       <c r="K16" t="n">
-        <v>13187</v>
+        <v>13241</v>
       </c>
       <c r="L16" t="n">
-        <v>303026</v>
+        <v>303146</v>
       </c>
       <c r="M16" t="n">
-        <v>647549</v>
+        <v>650530</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1092,25 +1092,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>247</v>
+        <v>311</v>
       </c>
       <c r="C16" t="n">
-        <v>195</v>
+        <v>261</v>
       </c>
       <c r="D16" t="n">
-        <v>55.9</v>
+        <v>54.4</v>
       </c>
       <c r="E16" t="n">
-        <v>266</v>
+        <v>340</v>
       </c>
       <c r="F16" t="n">
-        <v>220</v>
+        <v>318</v>
       </c>
       <c r="G16" t="n">
-        <v>297</v>
+        <v>372</v>
       </c>
       <c r="H16" t="n">
-        <v>234</v>
+        <v>350</v>
       </c>
       <c r="I16" t="n">
         <v>504</v>
@@ -1119,7 +1119,7 @@
         <v>19777</v>
       </c>
       <c r="K16" t="n">
-        <v>13241</v>
+        <v>13305</v>
       </c>
       <c r="L16" t="n">
         <v>303146</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1027,19 +1027,19 @@
         <v>604</v>
       </c>
       <c r="I14" t="n">
-        <v>5491</v>
+        <v>5530</v>
       </c>
       <c r="J14" t="n">
-        <v>41195</v>
+        <v>41549</v>
       </c>
       <c r="K14" t="n">
         <v>12147</v>
       </c>
       <c r="L14" t="n">
-        <v>293779</v>
+        <v>293818</v>
       </c>
       <c r="M14" t="n">
-        <v>526053</v>
+        <v>526407</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>8863</v>
+        <v>9737</v>
       </c>
       <c r="J15" t="n">
-        <v>104700</v>
+        <v>114212</v>
       </c>
       <c r="K15" t="n">
         <v>12994</v>
       </c>
       <c r="L15" t="n">
-        <v>302642</v>
+        <v>303555</v>
       </c>
       <c r="M15" t="n">
-        <v>630753</v>
+        <v>640619</v>
       </c>
     </row>
     <row r="16">
@@ -1092,40 +1092,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>311</v>
+        <v>332</v>
       </c>
       <c r="C16" t="n">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="D16" t="n">
         <v>54.4</v>
       </c>
       <c r="E16" t="n">
-        <v>340</v>
+        <v>366</v>
       </c>
       <c r="F16" t="n">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="G16" t="n">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="H16" t="n">
-        <v>350</v>
+        <v>384</v>
       </c>
       <c r="I16" t="n">
-        <v>504</v>
+        <v>965</v>
       </c>
       <c r="J16" t="n">
-        <v>19777</v>
+        <v>39365</v>
       </c>
       <c r="K16" t="n">
-        <v>13305</v>
+        <v>13326</v>
       </c>
       <c r="L16" t="n">
-        <v>303146</v>
+        <v>304520</v>
       </c>
       <c r="M16" t="n">
-        <v>650530</v>
+        <v>679984</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1027,19 +1027,19 @@
         <v>604</v>
       </c>
       <c r="I14" t="n">
-        <v>5530</v>
+        <v>5279</v>
       </c>
       <c r="J14" t="n">
-        <v>41549</v>
+        <v>41573</v>
       </c>
       <c r="K14" t="n">
         <v>12147</v>
       </c>
       <c r="L14" t="n">
-        <v>293818</v>
+        <v>293567</v>
       </c>
       <c r="M14" t="n">
-        <v>526407</v>
+        <v>526431</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>9737</v>
+        <v>9762</v>
       </c>
       <c r="J15" t="n">
-        <v>114212</v>
+        <v>115206</v>
       </c>
       <c r="K15" t="n">
         <v>12994</v>
       </c>
       <c r="L15" t="n">
-        <v>303555</v>
+        <v>303329</v>
       </c>
       <c r="M15" t="n">
-        <v>640619</v>
+        <v>641637</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>384</v>
       </c>
       <c r="I16" t="n">
-        <v>965</v>
+        <v>1126</v>
       </c>
       <c r="J16" t="n">
-        <v>39365</v>
+        <v>42746</v>
       </c>
       <c r="K16" t="n">
         <v>13326</v>
       </c>
       <c r="L16" t="n">
-        <v>304520</v>
+        <v>304455</v>
       </c>
       <c r="M16" t="n">
-        <v>679984</v>
+        <v>684383</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1027,19 +1027,19 @@
         <v>604</v>
       </c>
       <c r="I14" t="n">
-        <v>5279</v>
+        <v>4918</v>
       </c>
       <c r="J14" t="n">
-        <v>41573</v>
+        <v>40904</v>
       </c>
       <c r="K14" t="n">
         <v>12147</v>
       </c>
       <c r="L14" t="n">
-        <v>293567</v>
+        <v>293206</v>
       </c>
       <c r="M14" t="n">
-        <v>526431</v>
+        <v>525762</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>9762</v>
+        <v>9975</v>
       </c>
       <c r="J15" t="n">
-        <v>115206</v>
+        <v>116665</v>
       </c>
       <c r="K15" t="n">
         <v>12994</v>
       </c>
       <c r="L15" t="n">
-        <v>303329</v>
+        <v>303181</v>
       </c>
       <c r="M15" t="n">
-        <v>641637</v>
+        <v>642427</v>
       </c>
     </row>
     <row r="16">
@@ -1092,40 +1092,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C16" t="n">
-        <v>278</v>
+        <v>303</v>
       </c>
       <c r="D16" t="n">
-        <v>54.4</v>
+        <v>53.6</v>
       </c>
       <c r="E16" t="n">
-        <v>366</v>
+        <v>386</v>
       </c>
       <c r="F16" t="n">
-        <v>348</v>
+        <v>382</v>
       </c>
       <c r="G16" t="n">
-        <v>399</v>
+        <v>420</v>
       </c>
       <c r="H16" t="n">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="I16" t="n">
-        <v>1126</v>
+        <v>1282</v>
       </c>
       <c r="J16" t="n">
-        <v>42746</v>
+        <v>46921</v>
       </c>
       <c r="K16" t="n">
-        <v>13326</v>
+        <v>13344</v>
       </c>
       <c r="L16" t="n">
-        <v>304455</v>
+        <v>304463</v>
       </c>
       <c r="M16" t="n">
-        <v>684383</v>
+        <v>689348</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1092,25 +1092,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>350</v>
+        <v>375</v>
       </c>
       <c r="C16" t="n">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="D16" t="n">
-        <v>53.6</v>
+        <v>54.3</v>
       </c>
       <c r="E16" t="n">
-        <v>386</v>
+        <v>414</v>
       </c>
       <c r="F16" t="n">
-        <v>382</v>
+        <v>401</v>
       </c>
       <c r="G16" t="n">
-        <v>420</v>
+        <v>451</v>
       </c>
       <c r="H16" t="n">
-        <v>420</v>
+        <v>442</v>
       </c>
       <c r="I16" t="n">
         <v>1282</v>
@@ -1119,7 +1119,7 @@
         <v>46921</v>
       </c>
       <c r="K16" t="n">
-        <v>13344</v>
+        <v>13369</v>
       </c>
       <c r="L16" t="n">
         <v>304463</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1027,19 +1027,19 @@
         <v>604</v>
       </c>
       <c r="I14" t="n">
-        <v>4918</v>
+        <v>4764</v>
       </c>
       <c r="J14" t="n">
-        <v>40904</v>
+        <v>40527</v>
       </c>
       <c r="K14" t="n">
         <v>12147</v>
       </c>
       <c r="L14" t="n">
-        <v>293206</v>
+        <v>293052</v>
       </c>
       <c r="M14" t="n">
-        <v>525762</v>
+        <v>525385</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>9975</v>
+        <v>10231</v>
       </c>
       <c r="J15" t="n">
-        <v>116665</v>
+        <v>118738</v>
       </c>
       <c r="K15" t="n">
         <v>12994</v>
       </c>
       <c r="L15" t="n">
-        <v>303181</v>
+        <v>303283</v>
       </c>
       <c r="M15" t="n">
-        <v>642427</v>
+        <v>644123</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>442</v>
       </c>
       <c r="I16" t="n">
-        <v>1282</v>
+        <v>1581</v>
       </c>
       <c r="J16" t="n">
-        <v>46921</v>
+        <v>52784</v>
       </c>
       <c r="K16" t="n">
         <v>13369</v>
       </c>
       <c r="L16" t="n">
-        <v>304463</v>
+        <v>304864</v>
       </c>
       <c r="M16" t="n">
-        <v>689348</v>
+        <v>696907</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1092,37 +1092,37 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="C16" t="n">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="D16" t="n">
-        <v>54.3</v>
+        <v>53.8</v>
       </c>
       <c r="E16" t="n">
-        <v>414</v>
+        <v>430</v>
       </c>
       <c r="F16" t="n">
-        <v>401</v>
+        <v>425</v>
       </c>
       <c r="G16" t="n">
-        <v>451</v>
+        <v>467</v>
       </c>
       <c r="H16" t="n">
-        <v>442</v>
+        <v>471</v>
       </c>
       <c r="I16" t="n">
-        <v>1581</v>
+        <v>5273</v>
       </c>
       <c r="J16" t="n">
         <v>52784</v>
       </c>
       <c r="K16" t="n">
-        <v>13369</v>
+        <v>13380</v>
       </c>
       <c r="L16" t="n">
-        <v>304864</v>
+        <v>308556</v>
       </c>
       <c r="M16" t="n">
         <v>696907</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1027,19 +1027,19 @@
         <v>604</v>
       </c>
       <c r="I14" t="n">
-        <v>4764</v>
+        <v>3336</v>
       </c>
       <c r="J14" t="n">
-        <v>40527</v>
+        <v>35504</v>
       </c>
       <c r="K14" t="n">
         <v>12147</v>
       </c>
       <c r="L14" t="n">
-        <v>293052</v>
+        <v>291624</v>
       </c>
       <c r="M14" t="n">
-        <v>525385</v>
+        <v>520362</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>10231</v>
+        <v>11406</v>
       </c>
       <c r="J15" t="n">
-        <v>118738</v>
+        <v>128565</v>
       </c>
       <c r="K15" t="n">
         <v>12994</v>
       </c>
       <c r="L15" t="n">
-        <v>303283</v>
+        <v>303030</v>
       </c>
       <c r="M15" t="n">
-        <v>644123</v>
+        <v>648927</v>
       </c>
     </row>
     <row r="16">
@@ -1092,40 +1092,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>386</v>
+        <v>458</v>
       </c>
       <c r="C16" t="n">
-        <v>331</v>
+        <v>426</v>
       </c>
       <c r="D16" t="n">
-        <v>53.8</v>
+        <v>51.8</v>
       </c>
       <c r="E16" t="n">
-        <v>430</v>
+        <v>518</v>
       </c>
       <c r="F16" t="n">
-        <v>425</v>
+        <v>558</v>
       </c>
       <c r="G16" t="n">
-        <v>467</v>
+        <v>558</v>
       </c>
       <c r="H16" t="n">
-        <v>471</v>
+        <v>618</v>
       </c>
       <c r="I16" t="n">
-        <v>5273</v>
+        <v>6937</v>
       </c>
       <c r="J16" t="n">
-        <v>52784</v>
+        <v>81230</v>
       </c>
       <c r="K16" t="n">
-        <v>13380</v>
+        <v>13452</v>
       </c>
       <c r="L16" t="n">
-        <v>308556</v>
+        <v>309967</v>
       </c>
       <c r="M16" t="n">
-        <v>696907</v>
+        <v>730157</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1027,19 +1027,19 @@
         <v>604</v>
       </c>
       <c r="I14" t="n">
-        <v>3336</v>
+        <v>1649</v>
       </c>
       <c r="J14" t="n">
-        <v>35504</v>
+        <v>29782</v>
       </c>
       <c r="K14" t="n">
         <v>12147</v>
       </c>
       <c r="L14" t="n">
-        <v>291624</v>
+        <v>289937</v>
       </c>
       <c r="M14" t="n">
-        <v>520362</v>
+        <v>514640</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>11406</v>
+        <v>11604</v>
       </c>
       <c r="J15" t="n">
-        <v>128565</v>
+        <v>135864</v>
       </c>
       <c r="K15" t="n">
         <v>12994</v>
       </c>
       <c r="L15" t="n">
-        <v>303030</v>
+        <v>301541</v>
       </c>
       <c r="M15" t="n">
-        <v>648927</v>
+        <v>650504</v>
       </c>
     </row>
     <row r="16">
@@ -1092,40 +1092,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="C16" t="n">
-        <v>426</v>
+        <v>469</v>
       </c>
       <c r="D16" t="n">
-        <v>51.8</v>
+        <v>50.8</v>
       </c>
       <c r="E16" t="n">
-        <v>518</v>
+        <v>549</v>
       </c>
       <c r="F16" t="n">
-        <v>558</v>
+        <v>627</v>
       </c>
       <c r="G16" t="n">
-        <v>558</v>
+        <v>589</v>
       </c>
       <c r="H16" t="n">
-        <v>618</v>
+        <v>691</v>
       </c>
       <c r="I16" t="n">
-        <v>6937</v>
+        <v>7446</v>
       </c>
       <c r="J16" t="n">
-        <v>81230</v>
+        <v>85269</v>
       </c>
       <c r="K16" t="n">
-        <v>13452</v>
+        <v>13479</v>
       </c>
       <c r="L16" t="n">
-        <v>309967</v>
+        <v>308987</v>
       </c>
       <c r="M16" t="n">
-        <v>730157</v>
+        <v>735773</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1092,25 +1092,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>485</v>
+        <v>508</v>
       </c>
       <c r="C16" t="n">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="D16" t="n">
-        <v>50.8</v>
+        <v>51.3</v>
       </c>
       <c r="E16" t="n">
-        <v>549</v>
+        <v>587</v>
       </c>
       <c r="F16" t="n">
-        <v>627</v>
+        <v>650</v>
       </c>
       <c r="G16" t="n">
-        <v>589</v>
+        <v>632</v>
       </c>
       <c r="H16" t="n">
-        <v>691</v>
+        <v>719</v>
       </c>
       <c r="I16" t="n">
         <v>7446</v>
@@ -1119,7 +1119,7 @@
         <v>85269</v>
       </c>
       <c r="K16" t="n">
-        <v>13479</v>
+        <v>13502</v>
       </c>
       <c r="L16" t="n">
         <v>308987</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1,40 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>New_creators</t>
+  </si>
+  <si>
+    <t>Old_creators</t>
+  </si>
+  <si>
+    <t>New_share_pct</t>
+  </si>
+  <si>
+    <t>Sample_orders_new</t>
+  </si>
+  <si>
+    <t>Sample_orders_old</t>
+  </si>
+  <si>
+    <t>Sample_units_new</t>
+  </si>
+  <si>
+    <t>Sample_units_old</t>
+  </si>
+  <si>
+    <t>Video_GMV_new</t>
+  </si>
+  <si>
+    <t>Video_GMV_old</t>
+  </si>
+  <si>
+    <t>Cum_new_creators</t>
+  </si>
+  <si>
+    <t>Cum_GMV_new</t>
+  </si>
+  <si>
+    <t>Cum_GMV_old</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +140,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,727 +457,708 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:M17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>New_creators</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Old_creators</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>New_share_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Sample_orders_new</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Sample_orders_old</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Sample_units_new</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sample_units_old</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Video_GMV_new</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Video_GMV_old</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Cum_new_creators</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_new</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_old</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
         <v>70</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>70</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>70</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <v>2730</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>70</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>2730</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>41</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>41</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>41</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>6899</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>10092</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>111</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>9629</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>10092</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
         <v>432</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>432</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>433</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>62850</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>11972</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>543</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>72479</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>22064</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>568</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>100</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>568</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>568</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>6258</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>56244</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1111</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>78737</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>78308</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>629</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>100</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>629</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>629</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>11071</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>49346</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>1740</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>89808</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>127654</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>431</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>99.8</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>431</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>431</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>2171</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>37862</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>2171</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>91979</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>165516</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>811</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>8</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>99</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>818</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>8</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>891</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>15</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>11103</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>10409</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>2982</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>103082</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>175925</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>821</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>19</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>97.7</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>856</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>21</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1033</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>28</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>12312</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>32847</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>3803</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>115394</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>208772</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>1486</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>28</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>98.2</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1501</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>31</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1580</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>32</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>73914</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>62642</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>5289</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>189308</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>271414</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
         <v>877</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>93</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>90.40000000000001</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>890</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>99</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>894</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>105</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>68334</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>35898</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6166</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>257642</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>307312</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
         <v>587</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>392</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>60</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>689</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>447</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>699</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>451</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>12385</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>49429</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>6753</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>270027</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>356741</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
         <v>3026</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>512</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>85.5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3153</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>644</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>3184</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>658</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>18261</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>128117</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>9779</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>288288</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>484858</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
         <v>2368</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>421</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>84.90000000000001</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>2453</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>569</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>2469</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>604</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>1649</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>29782</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>12147</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>289937</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>514640</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
         <v>847</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>797</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>51.5</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>1117</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1298</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>1268</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1511</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>11604</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>135864</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>12994</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>301541</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>650504</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
         <v>508</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>482</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>51.3</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>587</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>650</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>632</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>719</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>7446</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>85269</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>13502</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>308987</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>735773</v>
       </c>
     </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
+        <v>70</v>
+      </c>
+      <c r="C17">
+        <v>71</v>
+      </c>
+      <c r="D17">
+        <v>49.6</v>
+      </c>
+      <c r="E17">
+        <v>77</v>
+      </c>
+      <c r="F17">
+        <v>77</v>
+      </c>
+      <c r="G17">
+        <v>90</v>
+      </c>
+      <c r="H17">
+        <v>83</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>13572</v>
+      </c>
+      <c r="L17">
+        <v>308987</v>
+      </c>
+      <c r="M17">
+        <v>735773</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>12273</v>
+        <v>12316</v>
       </c>
       <c r="J15" t="n">
-        <v>134682</v>
+        <v>131476</v>
       </c>
       <c r="K15" t="n">
         <v>12995</v>
       </c>
       <c r="L15" t="n">
-        <v>302210</v>
+        <v>302253</v>
       </c>
       <c r="M15" t="n">
-        <v>649322</v>
+        <v>646116</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>717</v>
       </c>
       <c r="I16" t="n">
-        <v>9656</v>
+        <v>9812</v>
       </c>
       <c r="J16" t="n">
-        <v>98348</v>
+        <v>100404</v>
       </c>
       <c r="K16" t="n">
         <v>13508</v>
       </c>
       <c r="L16" t="n">
-        <v>311866</v>
+        <v>312065</v>
       </c>
       <c r="M16" t="n">
-        <v>747670</v>
+        <v>746520</v>
       </c>
     </row>
     <row r="17">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="C17" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D17" t="n">
-        <v>62.2</v>
+        <v>50.6</v>
       </c>
       <c r="E17" t="n">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="F17" t="n">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="G17" t="n">
-        <v>182</v>
+        <v>99</v>
       </c>
       <c r="H17" t="n">
-        <v>167</v>
+        <v>95</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>4457</v>
+        <v>5520</v>
       </c>
       <c r="K17" t="n">
-        <v>13628</v>
+        <v>13587</v>
       </c>
       <c r="L17" t="n">
-        <v>311866</v>
+        <v>312065</v>
       </c>
       <c r="M17" t="n">
-        <v>752127</v>
+        <v>752040</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>12316</v>
+        <v>12288</v>
       </c>
       <c r="J15" t="n">
-        <v>131476</v>
+        <v>128479</v>
       </c>
       <c r="K15" t="n">
         <v>12995</v>
       </c>
       <c r="L15" t="n">
-        <v>302253</v>
+        <v>302225</v>
       </c>
       <c r="M15" t="n">
-        <v>646116</v>
+        <v>643119</v>
       </c>
     </row>
     <row r="16">
@@ -1092,40 +1092,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="C16" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="D16" t="n">
-        <v>51.6</v>
+        <v>51.7</v>
       </c>
       <c r="E16" t="n">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F16" t="n">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="G16" t="n">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="H16" t="n">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="I16" t="n">
-        <v>9812</v>
+        <v>10112</v>
       </c>
       <c r="J16" t="n">
-        <v>100404</v>
+        <v>101937</v>
       </c>
       <c r="K16" t="n">
-        <v>13508</v>
+        <v>13506</v>
       </c>
       <c r="L16" t="n">
-        <v>312065</v>
+        <v>312337</v>
       </c>
       <c r="M16" t="n">
-        <v>746520</v>
+        <v>745056</v>
       </c>
     </row>
     <row r="17">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="C17" t="n">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>50.6</v>
+        <v>48.3</v>
       </c>
       <c r="E17" t="n">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="F17" t="n">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="G17" t="n">
-        <v>99</v>
+        <v>141</v>
       </c>
       <c r="H17" t="n">
-        <v>95</v>
+        <v>154</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>5520</v>
+        <v>6640</v>
       </c>
       <c r="K17" t="n">
-        <v>13587</v>
+        <v>13617</v>
       </c>
       <c r="L17" t="n">
-        <v>312065</v>
+        <v>312337</v>
       </c>
       <c r="M17" t="n">
-        <v>752040</v>
+        <v>751696</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -877,37 +877,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D11" t="n">
-        <v>90.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="E11" t="n">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="F11" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G11" t="n">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="H11" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="I11" t="n">
-        <v>68334</v>
+        <v>68252</v>
       </c>
       <c r="J11" t="n">
         <v>35898</v>
       </c>
       <c r="K11" t="n">
-        <v>6167</v>
+        <v>6168</v>
       </c>
       <c r="L11" t="n">
-        <v>257642</v>
+        <v>257560</v>
       </c>
       <c r="M11" t="n">
         <v>307312</v>
@@ -920,40 +920,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C12" t="n">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>60.5</v>
       </c>
       <c r="E12" t="n">
-        <v>689</v>
+        <v>694</v>
       </c>
       <c r="F12" t="n">
-        <v>447</v>
+        <v>440</v>
       </c>
       <c r="G12" t="n">
-        <v>699</v>
+        <v>704</v>
       </c>
       <c r="H12" t="n">
-        <v>451</v>
+        <v>444</v>
       </c>
       <c r="I12" t="n">
-        <v>12385</v>
+        <v>12345</v>
       </c>
       <c r="J12" t="n">
-        <v>49429</v>
+        <v>49345</v>
       </c>
       <c r="K12" t="n">
-        <v>6754</v>
+        <v>6759</v>
       </c>
       <c r="L12" t="n">
-        <v>270027</v>
+        <v>269905</v>
       </c>
       <c r="M12" t="n">
-        <v>356741</v>
+        <v>356657</v>
       </c>
     </row>
     <row r="13">
@@ -963,40 +963,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3026</v>
+        <v>3024</v>
       </c>
       <c r="C13" t="n">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D13" t="n">
-        <v>85.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="F13" t="n">
-        <v>644</v>
+        <v>637</v>
       </c>
       <c r="G13" t="n">
-        <v>3184</v>
+        <v>3186</v>
       </c>
       <c r="H13" t="n">
-        <v>658</v>
+        <v>650</v>
       </c>
       <c r="I13" t="n">
-        <v>18261</v>
+        <v>18055</v>
       </c>
       <c r="J13" t="n">
-        <v>128117</v>
+        <v>128002</v>
       </c>
       <c r="K13" t="n">
-        <v>9780</v>
+        <v>9783</v>
       </c>
       <c r="L13" t="n">
-        <v>288288</v>
+        <v>287960</v>
       </c>
       <c r="M13" t="n">
-        <v>484858</v>
+        <v>484659</v>
       </c>
     </row>
     <row r="14">
@@ -1006,40 +1006,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2368</v>
+        <v>2365</v>
       </c>
       <c r="C14" t="n">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D14" t="n">
         <v>84.8</v>
       </c>
       <c r="E14" t="n">
-        <v>2453</v>
+        <v>2450</v>
       </c>
       <c r="F14" t="n">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="G14" t="n">
-        <v>2469</v>
+        <v>2466</v>
       </c>
       <c r="H14" t="n">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="I14" t="n">
-        <v>1649</v>
+        <v>1544</v>
       </c>
       <c r="J14" t="n">
-        <v>29782</v>
+        <v>29395</v>
       </c>
       <c r="K14" t="n">
         <v>12148</v>
       </c>
       <c r="L14" t="n">
-        <v>289937</v>
+        <v>289504</v>
       </c>
       <c r="M14" t="n">
-        <v>514640</v>
+        <v>514054</v>
       </c>
     </row>
     <row r="15">
@@ -1049,40 +1049,40 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C15" t="n">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D15" t="n">
-        <v>51.5</v>
+        <v>51.6</v>
       </c>
       <c r="E15" t="n">
         <v>1117</v>
       </c>
       <c r="F15" t="n">
-        <v>1298</v>
+        <v>1295</v>
       </c>
       <c r="G15" t="n">
         <v>1268</v>
       </c>
       <c r="H15" t="n">
-        <v>1511</v>
+        <v>1507</v>
       </c>
       <c r="I15" t="n">
-        <v>12288</v>
+        <v>12203</v>
       </c>
       <c r="J15" t="n">
-        <v>128479</v>
+        <v>127187</v>
       </c>
       <c r="K15" t="n">
-        <v>12995</v>
+        <v>12994</v>
       </c>
       <c r="L15" t="n">
-        <v>302225</v>
+        <v>301707</v>
       </c>
       <c r="M15" t="n">
-        <v>643119</v>
+        <v>641241</v>
       </c>
     </row>
     <row r="16">
@@ -1092,40 +1092,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>511</v>
+        <v>500</v>
       </c>
       <c r="C16" t="n">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="D16" t="n">
-        <v>51.7</v>
+        <v>50.6</v>
       </c>
       <c r="E16" t="n">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="F16" t="n">
-        <v>645</v>
+        <v>667</v>
       </c>
       <c r="G16" t="n">
-        <v>637</v>
+        <v>612</v>
       </c>
       <c r="H16" t="n">
-        <v>713</v>
+        <v>738</v>
       </c>
       <c r="I16" t="n">
-        <v>10112</v>
+        <v>3735</v>
       </c>
       <c r="J16" t="n">
-        <v>101937</v>
+        <v>107743</v>
       </c>
       <c r="K16" t="n">
-        <v>13506</v>
+        <v>13494</v>
       </c>
       <c r="L16" t="n">
-        <v>312337</v>
+        <v>305442</v>
       </c>
       <c r="M16" t="n">
-        <v>745056</v>
+        <v>748984</v>
       </c>
     </row>
     <row r="17">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C17" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D17" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="E17" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F17" t="n">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G17" t="n">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H17" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>6640</v>
+        <v>6682</v>
       </c>
       <c r="K17" t="n">
-        <v>13617</v>
+        <v>13604</v>
       </c>
       <c r="L17" t="n">
-        <v>312337</v>
+        <v>305442</v>
       </c>
       <c r="M17" t="n">
-        <v>751696</v>
+        <v>755666</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -877,37 +877,37 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C11" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D11" t="n">
-        <v>90.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="F11" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G11" t="n">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="H11" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I11" t="n">
-        <v>68252</v>
+        <v>68334</v>
       </c>
       <c r="J11" t="n">
         <v>35898</v>
       </c>
       <c r="K11" t="n">
-        <v>6168</v>
+        <v>6167</v>
       </c>
       <c r="L11" t="n">
-        <v>257560</v>
+        <v>257642</v>
       </c>
       <c r="M11" t="n">
         <v>307312</v>
@@ -920,40 +920,40 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="C12" t="n">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="D12" t="n">
-        <v>60.5</v>
+        <v>60</v>
       </c>
       <c r="E12" t="n">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="F12" t="n">
-        <v>440</v>
+        <v>447</v>
       </c>
       <c r="G12" t="n">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="H12" t="n">
-        <v>444</v>
+        <v>451</v>
       </c>
       <c r="I12" t="n">
-        <v>12345</v>
+        <v>12385</v>
       </c>
       <c r="J12" t="n">
-        <v>49345</v>
+        <v>49429</v>
       </c>
       <c r="K12" t="n">
-        <v>6759</v>
+        <v>6754</v>
       </c>
       <c r="L12" t="n">
-        <v>269905</v>
+        <v>270027</v>
       </c>
       <c r="M12" t="n">
-        <v>356657</v>
+        <v>356741</v>
       </c>
     </row>
     <row r="13">
@@ -963,40 +963,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3024</v>
+        <v>3026</v>
       </c>
       <c r="C13" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D13" t="n">
-        <v>85.59999999999999</v>
+        <v>85.5</v>
       </c>
       <c r="E13" t="n">
-        <v>3154</v>
+        <v>3153</v>
       </c>
       <c r="F13" t="n">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="G13" t="n">
-        <v>3186</v>
+        <v>3184</v>
       </c>
       <c r="H13" t="n">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="I13" t="n">
-        <v>18055</v>
+        <v>18261</v>
       </c>
       <c r="J13" t="n">
-        <v>128002</v>
+        <v>128117</v>
       </c>
       <c r="K13" t="n">
-        <v>9783</v>
+        <v>9780</v>
       </c>
       <c r="L13" t="n">
-        <v>287960</v>
+        <v>288288</v>
       </c>
       <c r="M13" t="n">
-        <v>484659</v>
+        <v>484858</v>
       </c>
     </row>
     <row r="14">
@@ -1006,40 +1006,40 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2365</v>
+        <v>2368</v>
       </c>
       <c r="C14" t="n">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D14" t="n">
         <v>84.8</v>
       </c>
       <c r="E14" t="n">
-        <v>2450</v>
+        <v>2453</v>
       </c>
       <c r="F14" t="n">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="G14" t="n">
-        <v>2466</v>
+        <v>2469</v>
       </c>
       <c r="H14" t="n">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="I14" t="n">
-        <v>1544</v>
+        <v>1649</v>
       </c>
       <c r="J14" t="n">
-        <v>29395</v>
+        <v>29782</v>
       </c>
       <c r="K14" t="n">
         <v>12148</v>
       </c>
       <c r="L14" t="n">
-        <v>289504</v>
+        <v>289937</v>
       </c>
       <c r="M14" t="n">
-        <v>514054</v>
+        <v>514640</v>
       </c>
     </row>
     <row r="15">
@@ -1049,10 +1049,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C15" t="n">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D15" t="n">
         <v>51.6</v>
@@ -1061,28 +1061,28 @@
         <v>1117</v>
       </c>
       <c r="F15" t="n">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="G15" t="n">
         <v>1268</v>
       </c>
       <c r="H15" t="n">
-        <v>1507</v>
+        <v>1510</v>
       </c>
       <c r="I15" t="n">
-        <v>12203</v>
+        <v>12288</v>
       </c>
       <c r="J15" t="n">
-        <v>127187</v>
+        <v>128479</v>
       </c>
       <c r="K15" t="n">
-        <v>12994</v>
+        <v>12995</v>
       </c>
       <c r="L15" t="n">
-        <v>301707</v>
+        <v>302225</v>
       </c>
       <c r="M15" t="n">
-        <v>641241</v>
+        <v>643119</v>
       </c>
     </row>
     <row r="16">
@@ -1092,40 +1092,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="C16" t="n">
-        <v>489</v>
+        <v>478</v>
       </c>
       <c r="D16" t="n">
-        <v>50.6</v>
+        <v>51.7</v>
       </c>
       <c r="E16" t="n">
-        <v>569</v>
+        <v>591</v>
       </c>
       <c r="F16" t="n">
-        <v>667</v>
+        <v>645</v>
       </c>
       <c r="G16" t="n">
-        <v>612</v>
+        <v>637</v>
       </c>
       <c r="H16" t="n">
-        <v>738</v>
+        <v>713</v>
       </c>
       <c r="I16" t="n">
-        <v>3735</v>
+        <v>10112</v>
       </c>
       <c r="J16" t="n">
-        <v>107743</v>
+        <v>101937</v>
       </c>
       <c r="K16" t="n">
-        <v>13494</v>
+        <v>13506</v>
       </c>
       <c r="L16" t="n">
-        <v>305442</v>
+        <v>312337</v>
       </c>
       <c r="M16" t="n">
-        <v>748984</v>
+        <v>745056</v>
       </c>
     </row>
     <row r="17">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="C17" t="n">
-        <v>121</v>
+        <v>173</v>
       </c>
       <c r="D17" t="n">
-        <v>47.6</v>
+        <v>43.3</v>
       </c>
       <c r="E17" t="n">
-        <v>121</v>
+        <v>150</v>
       </c>
       <c r="F17" t="n">
-        <v>139</v>
+        <v>204</v>
       </c>
       <c r="G17" t="n">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="H17" t="n">
-        <v>156</v>
+        <v>228</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>6682</v>
+        <v>6640</v>
       </c>
       <c r="K17" t="n">
-        <v>13604</v>
+        <v>13638</v>
       </c>
       <c r="L17" t="n">
-        <v>305442</v>
+        <v>312337</v>
       </c>
       <c r="M17" t="n">
-        <v>755666</v>
+        <v>751696</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1070,19 +1070,19 @@
         <v>1510</v>
       </c>
       <c r="I15" t="n">
-        <v>12288</v>
+        <v>12335</v>
       </c>
       <c r="J15" t="n">
-        <v>128479</v>
+        <v>125689</v>
       </c>
       <c r="K15" t="n">
         <v>12995</v>
       </c>
       <c r="L15" t="n">
-        <v>302225</v>
+        <v>302272</v>
       </c>
       <c r="M15" t="n">
-        <v>643119</v>
+        <v>640329</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>713</v>
       </c>
       <c r="I16" t="n">
-        <v>10112</v>
+        <v>10191</v>
       </c>
       <c r="J16" t="n">
-        <v>101937</v>
+        <v>103453</v>
       </c>
       <c r="K16" t="n">
         <v>13506</v>
       </c>
       <c r="L16" t="n">
-        <v>312337</v>
+        <v>312463</v>
       </c>
       <c r="M16" t="n">
-        <v>745056</v>
+        <v>743782</v>
       </c>
     </row>
     <row r="17">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="C17" t="n">
-        <v>173</v>
+        <v>249</v>
       </c>
       <c r="D17" t="n">
-        <v>43.3</v>
+        <v>37.4</v>
       </c>
       <c r="E17" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="F17" t="n">
-        <v>204</v>
+        <v>307</v>
       </c>
       <c r="G17" t="n">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="H17" t="n">
-        <v>228</v>
+        <v>360</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>6640</v>
+        <v>7548</v>
       </c>
       <c r="K17" t="n">
-        <v>13638</v>
+        <v>13655</v>
       </c>
       <c r="L17" t="n">
-        <v>312337</v>
+        <v>312463</v>
       </c>
       <c r="M17" t="n">
-        <v>751696</v>
+        <v>751330</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1070,19 +1070,19 @@
         <v>1510</v>
       </c>
       <c r="I15" t="n">
-        <v>12335</v>
+        <v>12303</v>
       </c>
       <c r="J15" t="n">
-        <v>125689</v>
+        <v>122593</v>
       </c>
       <c r="K15" t="n">
         <v>12995</v>
       </c>
       <c r="L15" t="n">
-        <v>302272</v>
+        <v>302240</v>
       </c>
       <c r="M15" t="n">
-        <v>640329</v>
+        <v>637233</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>713</v>
       </c>
       <c r="I16" t="n">
-        <v>10191</v>
+        <v>10289</v>
       </c>
       <c r="J16" t="n">
-        <v>103453</v>
+        <v>104406</v>
       </c>
       <c r="K16" t="n">
         <v>13506</v>
       </c>
       <c r="L16" t="n">
-        <v>312463</v>
+        <v>312529</v>
       </c>
       <c r="M16" t="n">
-        <v>743782</v>
+        <v>741639</v>
       </c>
     </row>
     <row r="17">
@@ -1159,16 +1159,16 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>7548</v>
+        <v>8465</v>
       </c>
       <c r="K17" t="n">
         <v>13655</v>
       </c>
       <c r="L17" t="n">
-        <v>312463</v>
+        <v>312529</v>
       </c>
       <c r="M17" t="n">
-        <v>751330</v>
+        <v>750104</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1070,19 +1070,19 @@
         <v>1510</v>
       </c>
       <c r="I15" t="n">
-        <v>12303</v>
+        <v>11791</v>
       </c>
       <c r="J15" t="n">
-        <v>122593</v>
+        <v>110148</v>
       </c>
       <c r="K15" t="n">
         <v>12995</v>
       </c>
       <c r="L15" t="n">
-        <v>302240</v>
+        <v>301728</v>
       </c>
       <c r="M15" t="n">
-        <v>637233</v>
+        <v>624788</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>713</v>
       </c>
       <c r="I16" t="n">
-        <v>10289</v>
+        <v>10508</v>
       </c>
       <c r="J16" t="n">
-        <v>104406</v>
+        <v>108000</v>
       </c>
       <c r="K16" t="n">
         <v>13506</v>
       </c>
       <c r="L16" t="n">
-        <v>312529</v>
+        <v>312236</v>
       </c>
       <c r="M16" t="n">
-        <v>741639</v>
+        <v>732788</v>
       </c>
     </row>
     <row r="17">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>149</v>
+        <v>310</v>
       </c>
       <c r="C17" t="n">
-        <v>249</v>
+        <v>483</v>
       </c>
       <c r="D17" t="n">
-        <v>37.4</v>
+        <v>39.1</v>
       </c>
       <c r="E17" t="n">
-        <v>169</v>
+        <v>358</v>
       </c>
       <c r="F17" t="n">
-        <v>307</v>
+        <v>601</v>
       </c>
       <c r="G17" t="n">
-        <v>192</v>
+        <v>408</v>
       </c>
       <c r="H17" t="n">
-        <v>360</v>
+        <v>698</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>8465</v>
+        <v>11835</v>
       </c>
       <c r="K17" t="n">
-        <v>13655</v>
+        <v>13816</v>
       </c>
       <c r="L17" t="n">
-        <v>312529</v>
+        <v>312236</v>
       </c>
       <c r="M17" t="n">
-        <v>750104</v>
+        <v>744623</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1135,25 +1135,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="C17" t="n">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="D17" t="n">
-        <v>39.1</v>
+        <v>39.7</v>
       </c>
       <c r="E17" t="n">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F17" t="n">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="G17" t="n">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="H17" t="n">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1162,7 +1162,7 @@
         <v>11835</v>
       </c>
       <c r="K17" t="n">
-        <v>13816</v>
+        <v>13827</v>
       </c>
       <c r="L17" t="n">
         <v>312236</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1,40 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>New_creators</t>
+  </si>
+  <si>
+    <t>Old_creators</t>
+  </si>
+  <si>
+    <t>New_share_pct</t>
+  </si>
+  <si>
+    <t>Sample_orders_new</t>
+  </si>
+  <si>
+    <t>Sample_orders_old</t>
+  </si>
+  <si>
+    <t>Sample_units_new</t>
+  </si>
+  <si>
+    <t>Sample_units_old</t>
+  </si>
+  <si>
+    <t>Video_GMV_new</t>
+  </si>
+  <si>
+    <t>Video_GMV_old</t>
+  </si>
+  <si>
+    <t>Cum_new_creators</t>
+  </si>
+  <si>
+    <t>Cum_GMV_new</t>
+  </si>
+  <si>
+    <t>Cum_GMV_old</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +140,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,770 +457,708 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>New_creators</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Old_creators</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>New_share_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Sample_orders_new</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Sample_orders_old</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Sample_units_new</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sample_units_old</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Video_GMV_new</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Video_GMV_old</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Cum_new_creators</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_new</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_old</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
         <v>70</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>70</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>70</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <v>2730</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>70</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>2730</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>41</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>41</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>41</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>6899</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>10092</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>111</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>9629</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>10092</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
         <v>432</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>432</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>433</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>62850</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>11972</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>543</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>72479</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>22064</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>568</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>100</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>568</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>568</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>6258</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>56244</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1111</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>78737</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>78308</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>629</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>100</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>629</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>629</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>11071</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>49346</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>1740</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>89808</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>127654</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>431</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>99.8</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>431</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>431</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>2171</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>37862</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>2171</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>91979</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>165516</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>812</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>8</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>99</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>819</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>8</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>892</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>15</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>11103</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>10409</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>2983</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>103082</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>175925</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>821</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>19</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>97.7</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>856</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>21</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1033</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>28</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>12312</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>32847</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>3804</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>115394</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>208772</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>1486</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>28</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>98.2</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1501</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>31</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1580</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>32</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>73914</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>62642</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>5290</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>189308</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>271414</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
         <v>877</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>93</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>90.40000000000001</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>890</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>99</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>894</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>105</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>68334</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>35898</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6167</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>257642</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>307312</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
         <v>587</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>392</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>60</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>689</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>447</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>699</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>451</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>12385</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>49429</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>6754</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>270027</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>356741</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
         <v>3026</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>512</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>85.5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3153</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>644</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>3184</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>658</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>18261</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>128117</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>9780</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>288288</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>484858</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
         <v>2368</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>424</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>84.8</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>2453</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>572</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>2469</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>607</v>
       </c>
-      <c r="I14" t="n">
-        <v>1649</v>
-      </c>
-      <c r="J14" t="n">
-        <v>29782</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="I14">
+        <v>2887</v>
+      </c>
+      <c r="J14">
+        <v>32511</v>
+      </c>
+      <c r="K14">
         <v>12148</v>
       </c>
-      <c r="L14" t="n">
-        <v>289937</v>
-      </c>
-      <c r="M14" t="n">
-        <v>514640</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+      <c r="L14">
+        <v>291175</v>
+      </c>
+      <c r="M14">
+        <v>517369</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
         <v>847</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>796</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>51.6</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>1117</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1297</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>1268</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1510</v>
       </c>
-      <c r="I15" t="n">
-        <v>11791</v>
-      </c>
-      <c r="J15" t="n">
-        <v>110148</v>
-      </c>
-      <c r="K15" t="n">
+      <c r="I15">
+        <v>11933</v>
+      </c>
+      <c r="J15">
+        <v>113416</v>
+      </c>
+      <c r="K15">
         <v>12995</v>
       </c>
-      <c r="L15" t="n">
-        <v>301728</v>
-      </c>
-      <c r="M15" t="n">
-        <v>624788</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+      <c r="L15">
+        <v>303108</v>
+      </c>
+      <c r="M15">
+        <v>630785</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
         <v>511</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>478</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>51.7</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>591</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>645</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>637</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>713</v>
       </c>
-      <c r="I16" t="n">
-        <v>10508</v>
-      </c>
-      <c r="J16" t="n">
-        <v>108000</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="I16">
+        <v>10515</v>
+      </c>
+      <c r="J16">
+        <v>108053</v>
+      </c>
+      <c r="K16">
         <v>13506</v>
       </c>
-      <c r="L16" t="n">
-        <v>312236</v>
-      </c>
-      <c r="M16" t="n">
-        <v>732788</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+      <c r="L16">
+        <v>313623</v>
+      </c>
+      <c r="M16">
+        <v>738838</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
         <v>321</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>487</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>39.7</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>369</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>608</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>419</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>705</v>
       </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>11835</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>11855</v>
+      </c>
+      <c r="K17">
         <v>13827</v>
       </c>
-      <c r="L17" t="n">
-        <v>312236</v>
-      </c>
-      <c r="M17" t="n">
-        <v>744623</v>
+      <c r="L17">
+        <v>313623</v>
+      </c>
+      <c r="M17">
+        <v>750693</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1122,25 +1122,25 @@
         <v>28</v>
       </c>
       <c r="B17">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="C17">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="D17">
-        <v>39.7</v>
+        <v>41.3</v>
       </c>
       <c r="E17">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="F17">
-        <v>608</v>
+        <v>624</v>
       </c>
       <c r="G17">
-        <v>419</v>
+        <v>456</v>
       </c>
       <c r="H17">
-        <v>705</v>
+        <v>721</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -1149,7 +1149,7 @@
         <v>11855</v>
       </c>
       <c r="K17">
-        <v>13827</v>
+        <v>13856</v>
       </c>
       <c r="L17">
         <v>313623</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1030,7 +1030,7 @@
         <v>2887</v>
       </c>
       <c r="J14" t="n">
-        <v>32543</v>
+        <v>32806</v>
       </c>
       <c r="K14" t="n">
         <v>12148</v>
@@ -1039,7 +1039,7 @@
         <v>291175</v>
       </c>
       <c r="M14" t="n">
-        <v>517401</v>
+        <v>517664</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>12970</v>
+        <v>12848</v>
       </c>
       <c r="J15" t="n">
-        <v>111439</v>
+        <v>109857</v>
       </c>
       <c r="K15" t="n">
         <v>12995</v>
       </c>
       <c r="L15" t="n">
-        <v>304145</v>
+        <v>304023</v>
       </c>
       <c r="M15" t="n">
-        <v>628840</v>
+        <v>627521</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>713</v>
       </c>
       <c r="I16" t="n">
-        <v>10644</v>
+        <v>10712</v>
       </c>
       <c r="J16" t="n">
-        <v>109527</v>
+        <v>110344</v>
       </c>
       <c r="K16" t="n">
         <v>13506</v>
       </c>
       <c r="L16" t="n">
-        <v>314789</v>
+        <v>314735</v>
       </c>
       <c r="M16" t="n">
-        <v>738367</v>
+        <v>737865</v>
       </c>
     </row>
     <row r="17">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>350</v>
+        <v>430</v>
       </c>
       <c r="C17" t="n">
-        <v>498</v>
+        <v>568</v>
       </c>
       <c r="D17" t="n">
-        <v>41.3</v>
+        <v>43.1</v>
       </c>
       <c r="E17" t="n">
-        <v>401</v>
+        <v>511</v>
       </c>
       <c r="F17" t="n">
-        <v>624</v>
+        <v>731</v>
       </c>
       <c r="G17" t="n">
-        <v>456</v>
+        <v>592</v>
       </c>
       <c r="H17" t="n">
-        <v>721</v>
+        <v>832</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="J17" t="n">
-        <v>13177</v>
+        <v>14518</v>
       </c>
       <c r="K17" t="n">
-        <v>13856</v>
+        <v>13936</v>
       </c>
       <c r="L17" t="n">
-        <v>314789</v>
+        <v>314780</v>
       </c>
       <c r="M17" t="n">
-        <v>751544</v>
+        <v>752383</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>12848</v>
+        <v>12722</v>
       </c>
       <c r="J15" t="n">
-        <v>109857</v>
+        <v>106758</v>
       </c>
       <c r="K15" t="n">
         <v>12995</v>
       </c>
       <c r="L15" t="n">
-        <v>304023</v>
+        <v>303897</v>
       </c>
       <c r="M15" t="n">
-        <v>627521</v>
+        <v>624422</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>713</v>
       </c>
       <c r="I16" t="n">
-        <v>10712</v>
+        <v>10778</v>
       </c>
       <c r="J16" t="n">
-        <v>110344</v>
+        <v>112282</v>
       </c>
       <c r="K16" t="n">
         <v>13506</v>
       </c>
       <c r="L16" t="n">
-        <v>314735</v>
+        <v>314675</v>
       </c>
       <c r="M16" t="n">
-        <v>737865</v>
+        <v>736704</v>
       </c>
     </row>
     <row r="17">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>430</v>
+        <v>480</v>
       </c>
       <c r="C17" t="n">
-        <v>568</v>
+        <v>634</v>
       </c>
       <c r="D17" t="n">
         <v>43.1</v>
       </c>
       <c r="E17" t="n">
-        <v>511</v>
+        <v>579</v>
       </c>
       <c r="F17" t="n">
-        <v>731</v>
+        <v>866</v>
       </c>
       <c r="G17" t="n">
-        <v>592</v>
+        <v>674</v>
       </c>
       <c r="H17" t="n">
-        <v>832</v>
+        <v>976</v>
       </c>
       <c r="I17" t="n">
         <v>45</v>
       </c>
       <c r="J17" t="n">
-        <v>14518</v>
+        <v>16241</v>
       </c>
       <c r="K17" t="n">
-        <v>13936</v>
+        <v>13986</v>
       </c>
       <c r="L17" t="n">
-        <v>314780</v>
+        <v>314720</v>
       </c>
       <c r="M17" t="n">
-        <v>752383</v>
+        <v>752945</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1027,19 +1027,19 @@
         <v>607</v>
       </c>
       <c r="I14" t="n">
-        <v>2887</v>
+        <v>2922</v>
       </c>
       <c r="J14" t="n">
-        <v>32806</v>
+        <v>32851</v>
       </c>
       <c r="K14" t="n">
         <v>12148</v>
       </c>
       <c r="L14" t="n">
-        <v>291175</v>
+        <v>291210</v>
       </c>
       <c r="M14" t="n">
-        <v>517664</v>
+        <v>517709</v>
       </c>
     </row>
     <row r="15">
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>12722</v>
+        <v>12103</v>
       </c>
       <c r="J15" t="n">
-        <v>106758</v>
+        <v>99032</v>
       </c>
       <c r="K15" t="n">
         <v>12995</v>
       </c>
       <c r="L15" t="n">
-        <v>303897</v>
+        <v>303313</v>
       </c>
       <c r="M15" t="n">
-        <v>624422</v>
+        <v>616741</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>713</v>
       </c>
       <c r="I16" t="n">
-        <v>10778</v>
+        <v>10899</v>
       </c>
       <c r="J16" t="n">
-        <v>112282</v>
+        <v>115317</v>
       </c>
       <c r="K16" t="n">
         <v>13506</v>
       </c>
       <c r="L16" t="n">
-        <v>314675</v>
+        <v>314212</v>
       </c>
       <c r="M16" t="n">
-        <v>736704</v>
+        <v>732058</v>
       </c>
     </row>
     <row r="17">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>480</v>
+        <v>726</v>
       </c>
       <c r="C17" t="n">
-        <v>634</v>
+        <v>771</v>
       </c>
       <c r="D17" t="n">
-        <v>43.1</v>
+        <v>48.5</v>
       </c>
       <c r="E17" t="n">
-        <v>579</v>
+        <v>894</v>
       </c>
       <c r="F17" t="n">
-        <v>866</v>
+        <v>1085</v>
       </c>
       <c r="G17" t="n">
-        <v>674</v>
+        <v>1013</v>
       </c>
       <c r="H17" t="n">
-        <v>976</v>
+        <v>1221</v>
       </c>
       <c r="I17" t="n">
-        <v>45</v>
+        <v>304</v>
       </c>
       <c r="J17" t="n">
-        <v>16241</v>
+        <v>20705</v>
       </c>
       <c r="K17" t="n">
-        <v>13986</v>
+        <v>14232</v>
       </c>
       <c r="L17" t="n">
-        <v>314720</v>
+        <v>314516</v>
       </c>
       <c r="M17" t="n">
-        <v>752945</v>
+        <v>752763</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1135,25 +1135,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>726</v>
+        <v>768</v>
       </c>
       <c r="C17" t="n">
-        <v>771</v>
+        <v>801</v>
       </c>
       <c r="D17" t="n">
-        <v>48.5</v>
+        <v>48.9</v>
       </c>
       <c r="E17" t="n">
-        <v>894</v>
+        <v>949</v>
       </c>
       <c r="F17" t="n">
-        <v>1085</v>
+        <v>1139</v>
       </c>
       <c r="G17" t="n">
-        <v>1013</v>
+        <v>1071</v>
       </c>
       <c r="H17" t="n">
-        <v>1221</v>
+        <v>1276</v>
       </c>
       <c r="I17" t="n">
         <v>304</v>
@@ -1162,7 +1162,7 @@
         <v>20705</v>
       </c>
       <c r="K17" t="n">
-        <v>14232</v>
+        <v>14274</v>
       </c>
       <c r="L17" t="n">
         <v>314516</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1135,25 +1135,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>768</v>
+        <v>837</v>
       </c>
       <c r="C17" t="n">
-        <v>801</v>
+        <v>836</v>
       </c>
       <c r="D17" t="n">
-        <v>48.9</v>
+        <v>50</v>
       </c>
       <c r="E17" t="n">
-        <v>949</v>
+        <v>1044</v>
       </c>
       <c r="F17" t="n">
-        <v>1139</v>
+        <v>1198</v>
       </c>
       <c r="G17" t="n">
-        <v>1071</v>
+        <v>1179</v>
       </c>
       <c r="H17" t="n">
-        <v>1276</v>
+        <v>1336</v>
       </c>
       <c r="I17" t="n">
         <v>304</v>
@@ -1162,7 +1162,7 @@
         <v>20705</v>
       </c>
       <c r="K17" t="n">
-        <v>14274</v>
+        <v>14343</v>
       </c>
       <c r="L17" t="n">
         <v>314516</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1027,7 +1027,7 @@
         <v>607</v>
       </c>
       <c r="I14" t="n">
-        <v>2922</v>
+        <v>2943</v>
       </c>
       <c r="J14" t="n">
         <v>32851</v>
@@ -1036,7 +1036,7 @@
         <v>12148</v>
       </c>
       <c r="L14" t="n">
-        <v>291210</v>
+        <v>291231</v>
       </c>
       <c r="M14" t="n">
         <v>517709</v>
@@ -1070,19 +1070,19 @@
         <v>1511</v>
       </c>
       <c r="I15" t="n">
-        <v>12103</v>
+        <v>11865</v>
       </c>
       <c r="J15" t="n">
-        <v>99032</v>
+        <v>94465</v>
       </c>
       <c r="K15" t="n">
         <v>12995</v>
       </c>
       <c r="L15" t="n">
-        <v>303313</v>
+        <v>303096</v>
       </c>
       <c r="M15" t="n">
-        <v>616741</v>
+        <v>612174</v>
       </c>
     </row>
     <row r="16">
@@ -1113,19 +1113,19 @@
         <v>713</v>
       </c>
       <c r="I16" t="n">
-        <v>10899</v>
+        <v>10983</v>
       </c>
       <c r="J16" t="n">
-        <v>115317</v>
+        <v>117574</v>
       </c>
       <c r="K16" t="n">
         <v>13506</v>
       </c>
       <c r="L16" t="n">
-        <v>314212</v>
+        <v>314079</v>
       </c>
       <c r="M16" t="n">
-        <v>732058</v>
+        <v>729748</v>
       </c>
     </row>
     <row r="17">
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>837</v>
+        <v>941</v>
       </c>
       <c r="C17" t="n">
-        <v>836</v>
+        <v>904</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" t="n">
-        <v>1044</v>
+        <v>1183</v>
       </c>
       <c r="F17" t="n">
-        <v>1198</v>
+        <v>1325</v>
       </c>
       <c r="G17" t="n">
-        <v>1179</v>
+        <v>1334</v>
       </c>
       <c r="H17" t="n">
-        <v>1336</v>
+        <v>1471</v>
       </c>
       <c r="I17" t="n">
-        <v>304</v>
+        <v>488</v>
       </c>
       <c r="J17" t="n">
-        <v>20705</v>
+        <v>23983</v>
       </c>
       <c r="K17" t="n">
-        <v>14343</v>
+        <v>14447</v>
       </c>
       <c r="L17" t="n">
-        <v>314516</v>
+        <v>314567</v>
       </c>
       <c r="M17" t="n">
-        <v>752763</v>
+        <v>753731</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1,40 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>New_creators</t>
+  </si>
+  <si>
+    <t>Old_creators</t>
+  </si>
+  <si>
+    <t>New_share_pct</t>
+  </si>
+  <si>
+    <t>Sample_orders_new</t>
+  </si>
+  <si>
+    <t>Sample_orders_old</t>
+  </si>
+  <si>
+    <t>Sample_units_new</t>
+  </si>
+  <si>
+    <t>Sample_units_old</t>
+  </si>
+  <si>
+    <t>Video_GMV_new</t>
+  </si>
+  <si>
+    <t>Video_GMV_old</t>
+  </si>
+  <si>
+    <t>Cum_new_creators</t>
+  </si>
+  <si>
+    <t>Cum_GMV_new</t>
+  </si>
+  <si>
+    <t>Cum_GMV_old</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +140,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,770 +457,708 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>New_creators</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Old_creators</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>New_share_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Sample_orders_new</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Sample_orders_old</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Sample_units_new</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sample_units_old</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Video_GMV_new</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Video_GMV_old</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Cum_new_creators</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_new</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_old</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
         <v>70</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>70</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>70</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <v>2730</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>70</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>2730</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>41</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>41</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>41</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>6899</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>10092</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>111</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>9629</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>10092</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
         <v>432</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>432</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>433</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>62850</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>11972</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>543</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>72479</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>22064</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>568</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>100</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>568</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>568</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>6258</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>56244</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1111</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>78737</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>78308</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>629</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>100</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>629</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>629</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>11071</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>49346</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>1740</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>89808</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>127654</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>431</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>99.8</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>431</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>431</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>2171</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>37862</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>2171</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>91979</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>165516</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>812</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>8</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>99</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>819</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>8</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>892</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>15</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>11103</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>10409</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>2983</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>103082</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>175925</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>821</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>19</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>97.7</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>856</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>21</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1033</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>28</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>12312</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>32847</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>3804</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>115394</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>208772</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>1486</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>28</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>98.2</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1501</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>31</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1580</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>32</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>73914</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>62642</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>5290</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>189308</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>271414</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
         <v>877</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>93</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>90.40000000000001</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>890</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>99</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>894</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>105</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>68334</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>35898</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6167</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>257642</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>307312</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
         <v>587</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>392</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>60</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>689</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>447</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>699</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>451</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>12385</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>49429</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>6754</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>270027</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>356741</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
         <v>3026</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>512</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>85.5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3153</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>644</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>3184</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>658</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>18261</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>128117</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>9780</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>288288</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>484858</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
         <v>2368</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>424</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>84.8</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>2453</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>572</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>2469</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>607</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>2943</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>32851</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>12148</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>291231</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>517709</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
         <v>847</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>797</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>51.5</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>1117</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1298</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>1268</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1511</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>11865</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>94465</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>12995</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>303096</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>612174</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
         <v>511</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>478</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>51.7</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>591</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>645</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>637</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>713</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>10983</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>117574</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>13506</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>314079</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>729748</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
         <v>941</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>904</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>51</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>1183</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>1325</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>1334</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>1471</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>488</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>23983</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>14447</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>314567</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>753731</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1122,25 +1122,25 @@
         <v>28</v>
       </c>
       <c r="B17">
-        <v>941</v>
+        <v>1012</v>
       </c>
       <c r="C17">
-        <v>904</v>
+        <v>968</v>
       </c>
       <c r="D17">
-        <v>51</v>
+        <v>51.1</v>
       </c>
       <c r="E17">
-        <v>1183</v>
+        <v>1284</v>
       </c>
       <c r="F17">
-        <v>1325</v>
+        <v>1431</v>
       </c>
       <c r="G17">
-        <v>1334</v>
+        <v>1436</v>
       </c>
       <c r="H17">
-        <v>1471</v>
+        <v>1579</v>
       </c>
       <c r="I17">
         <v>488</v>
@@ -1149,7 +1149,7 @@
         <v>23983</v>
       </c>
       <c r="K17">
-        <v>14447</v>
+        <v>14518</v>
       </c>
       <c r="L17">
         <v>314567</v>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1,40 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>New_creators</t>
+  </si>
+  <si>
+    <t>Old_creators</t>
+  </si>
+  <si>
+    <t>New_share_pct</t>
+  </si>
+  <si>
+    <t>Sample_orders_new</t>
+  </si>
+  <si>
+    <t>Sample_orders_old</t>
+  </si>
+  <si>
+    <t>Sample_units_new</t>
+  </si>
+  <si>
+    <t>Sample_units_old</t>
+  </si>
+  <si>
+    <t>Video_GMV_new</t>
+  </si>
+  <si>
+    <t>Video_GMV_old</t>
+  </si>
+  <si>
+    <t>Cum_new_creators</t>
+  </si>
+  <si>
+    <t>Cum_GMV_new</t>
+  </si>
+  <si>
+    <t>Cum_GMV_old</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +140,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,770 +457,708 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>New_creators</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Old_creators</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>New_share_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Sample_orders_new</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Sample_orders_old</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Sample_units_new</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sample_units_old</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Video_GMV_new</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Video_GMV_old</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Cum_new_creators</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_new</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_old</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
         <v>70</v>
       </c>
-      <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>70</v>
       </c>
-      <c r="F2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>70</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
         <v>2730</v>
       </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
         <v>70</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>2730</v>
       </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="M2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>41</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>41</v>
       </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>41</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
         <v>6899</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>10092</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>111</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>9629</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>10092</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
         <v>432</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>432</v>
       </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>433</v>
       </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>62850</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>11972</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>543</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>72479</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>22064</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>568</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
         <v>100</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>568</v>
       </c>
-      <c r="F5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>568</v>
       </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>6258</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>56244</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1111</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>78737</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>78308</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>629</v>
       </c>
-      <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>100</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>629</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>629</v>
       </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6">
         <v>11071</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>49346</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>1740</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>89808</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>127654</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>431</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>99.8</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>431</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>1</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>431</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>1</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>2171</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>37862</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>2171</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>91979</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>165516</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>812</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>8</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>99</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>819</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>8</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>892</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>15</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>11103</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>10409</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>2983</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>103082</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>175925</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>821</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>19</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>97.7</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>856</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>21</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1033</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>28</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>12312</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>32847</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>3804</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>115394</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>208772</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>1486</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>28</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>98.2</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1501</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>31</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1580</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>32</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>73914</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>62642</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>5290</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>189308</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>271414</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
         <v>877</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>93</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>90.40000000000001</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>890</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>99</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>894</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>105</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>68334</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>35898</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6167</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>257642</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>307312</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
         <v>587</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>392</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>60</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>689</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>447</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>699</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>451</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>12385</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>49429</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>6754</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>270027</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>356741</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
         <v>3026</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>512</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>85.5</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3153</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>644</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>3184</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>658</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>18261</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>128117</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>9780</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>288288</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>484858</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
         <v>2368</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>424</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>84.8</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>2453</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>572</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>2469</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>607</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>2943</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>33226</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>12148</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>291231</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>518084</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
         <v>847</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>797</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>51.5</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>1117</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1298</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>1268</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1511</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>11697</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>91389</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>12995</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>302928</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>609473</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
         <v>511</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>478</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>51.7</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>591</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>645</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>637</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>713</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>11045</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>119130</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>13506</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>313973</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>728603</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
         <v>1012</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>968</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>51.1</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>1284</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>1431</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>1436</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>1579</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>613</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>26458</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>14518</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>314586</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>755061</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -712,7 +712,7 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -721,13 +721,13 @@
         <v>99.8</v>
       </c>
       <c r="E7">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -739,7 +739,7 @@
         <v>37862</v>
       </c>
       <c r="K7">
-        <v>2171</v>
+        <v>2169</v>
       </c>
       <c r="L7">
         <v>91979</v>
@@ -780,7 +780,7 @@
         <v>10409</v>
       </c>
       <c r="K8">
-        <v>2983</v>
+        <v>2981</v>
       </c>
       <c r="L8">
         <v>103082</v>
@@ -821,7 +821,7 @@
         <v>32847</v>
       </c>
       <c r="K9">
-        <v>3804</v>
+        <v>3802</v>
       </c>
       <c r="L9">
         <v>115394</v>
@@ -838,22 +838,22 @@
         <v>1486</v>
       </c>
       <c r="C10">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D10">
-        <v>98.2</v>
+        <v>98.3</v>
       </c>
       <c r="E10">
         <v>1501</v>
       </c>
       <c r="F10">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G10">
         <v>1580</v>
       </c>
       <c r="H10">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I10">
         <v>73914</v>
@@ -862,7 +862,7 @@
         <v>62642</v>
       </c>
       <c r="K10">
-        <v>5290</v>
+        <v>5288</v>
       </c>
       <c r="L10">
         <v>189308</v>
@@ -876,25 +876,25 @@
         <v>22</v>
       </c>
       <c r="B11">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C11">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D11">
-        <v>90.40000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="E11">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="F11">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G11">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="H11">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I11">
         <v>68334</v>
@@ -903,7 +903,7 @@
         <v>35898</v>
       </c>
       <c r="K11">
-        <v>6167</v>
+        <v>6164</v>
       </c>
       <c r="L11">
         <v>257642</v>
@@ -917,22 +917,22 @@
         <v>23</v>
       </c>
       <c r="B12">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="C12">
         <v>392</v>
       </c>
       <c r="D12">
-        <v>60</v>
+        <v>59.3</v>
       </c>
       <c r="E12">
-        <v>689</v>
+        <v>672</v>
       </c>
       <c r="F12">
         <v>447</v>
       </c>
       <c r="G12">
-        <v>699</v>
+        <v>682</v>
       </c>
       <c r="H12">
         <v>451</v>
@@ -944,7 +944,7 @@
         <v>49429</v>
       </c>
       <c r="K12">
-        <v>6754</v>
+        <v>6735</v>
       </c>
       <c r="L12">
         <v>270027</v>
@@ -958,25 +958,25 @@
         <v>24</v>
       </c>
       <c r="B13">
-        <v>3026</v>
+        <v>2975</v>
       </c>
       <c r="C13">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D13">
-        <v>85.5</v>
+        <v>85.3</v>
       </c>
       <c r="E13">
-        <v>3153</v>
+        <v>3095</v>
       </c>
       <c r="F13">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="G13">
-        <v>3184</v>
+        <v>3126</v>
       </c>
       <c r="H13">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="I13">
         <v>18261</v>
@@ -985,7 +985,7 @@
         <v>128117</v>
       </c>
       <c r="K13">
-        <v>9780</v>
+        <v>9710</v>
       </c>
       <c r="L13">
         <v>288288</v>
@@ -999,40 +999,40 @@
         <v>25</v>
       </c>
       <c r="B14">
-        <v>2368</v>
+        <v>1760</v>
       </c>
       <c r="C14">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="D14">
-        <v>84.8</v>
+        <v>81</v>
       </c>
       <c r="E14">
-        <v>2453</v>
+        <v>1837</v>
       </c>
       <c r="F14">
-        <v>572</v>
+        <v>562</v>
       </c>
       <c r="G14">
-        <v>2469</v>
+        <v>1853</v>
       </c>
       <c r="H14">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="I14">
-        <v>2943</v>
+        <v>3025</v>
       </c>
       <c r="J14">
-        <v>33226</v>
+        <v>33334</v>
       </c>
       <c r="K14">
-        <v>12148</v>
+        <v>11470</v>
       </c>
       <c r="L14">
-        <v>291231</v>
+        <v>291313</v>
       </c>
       <c r="M14">
-        <v>518084</v>
+        <v>518192</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1040,40 +1040,40 @@
         <v>26</v>
       </c>
       <c r="B15">
-        <v>847</v>
+        <v>519</v>
       </c>
       <c r="C15">
-        <v>797</v>
+        <v>789</v>
       </c>
       <c r="D15">
-        <v>51.5</v>
+        <v>39.7</v>
       </c>
       <c r="E15">
-        <v>1117</v>
+        <v>788</v>
       </c>
       <c r="F15">
-        <v>1298</v>
+        <v>1289</v>
       </c>
       <c r="G15">
-        <v>1268</v>
+        <v>939</v>
       </c>
       <c r="H15">
-        <v>1511</v>
+        <v>1502</v>
       </c>
       <c r="I15">
-        <v>11697</v>
+        <v>11817</v>
       </c>
       <c r="J15">
-        <v>91389</v>
+        <v>88558</v>
       </c>
       <c r="K15">
-        <v>12995</v>
+        <v>11989</v>
       </c>
       <c r="L15">
-        <v>302928</v>
+        <v>303130</v>
       </c>
       <c r="M15">
-        <v>609473</v>
+        <v>606750</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1081,40 +1081,40 @@
         <v>27</v>
       </c>
       <c r="B16">
-        <v>511</v>
+        <v>331</v>
       </c>
       <c r="C16">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="D16">
-        <v>51.7</v>
+        <v>41.6</v>
       </c>
       <c r="E16">
-        <v>591</v>
+        <v>409</v>
       </c>
       <c r="F16">
-        <v>645</v>
+        <v>629</v>
       </c>
       <c r="G16">
-        <v>637</v>
+        <v>455</v>
       </c>
       <c r="H16">
-        <v>713</v>
+        <v>697</v>
       </c>
       <c r="I16">
-        <v>11045</v>
+        <v>11060</v>
       </c>
       <c r="J16">
-        <v>119130</v>
+        <v>117955</v>
       </c>
       <c r="K16">
-        <v>13506</v>
+        <v>12320</v>
       </c>
       <c r="L16">
-        <v>313973</v>
+        <v>314190</v>
       </c>
       <c r="M16">
-        <v>728603</v>
+        <v>724705</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1122,40 +1122,40 @@
         <v>28</v>
       </c>
       <c r="B17">
-        <v>1012</v>
+        <v>871</v>
       </c>
       <c r="C17">
-        <v>968</v>
+        <v>946</v>
       </c>
       <c r="D17">
-        <v>51.1</v>
+        <v>47.9</v>
       </c>
       <c r="E17">
-        <v>1284</v>
+        <v>1140</v>
       </c>
       <c r="F17">
-        <v>1431</v>
+        <v>1409</v>
       </c>
       <c r="G17">
-        <v>1436</v>
+        <v>1292</v>
       </c>
       <c r="H17">
-        <v>1579</v>
+        <v>1557</v>
       </c>
       <c r="I17">
-        <v>613</v>
+        <v>638</v>
       </c>
       <c r="J17">
-        <v>26458</v>
+        <v>26615</v>
       </c>
       <c r="K17">
-        <v>14518</v>
+        <v>13191</v>
       </c>
       <c r="L17">
-        <v>314586</v>
+        <v>314828</v>
       </c>
       <c r="M17">
-        <v>755061</v>
+        <v>751320</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1064,7 +1064,7 @@
         <v>11817</v>
       </c>
       <c r="J15">
-        <v>88558</v>
+        <v>88451</v>
       </c>
       <c r="K15">
         <v>11989</v>
@@ -1073,7 +1073,7 @@
         <v>303130</v>
       </c>
       <c r="M15">
-        <v>606750</v>
+        <v>606643</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1105,7 +1105,7 @@
         <v>11060</v>
       </c>
       <c r="J16">
-        <v>117955</v>
+        <v>117962</v>
       </c>
       <c r="K16">
         <v>12320</v>
@@ -1114,7 +1114,7 @@
         <v>314190</v>
       </c>
       <c r="M16">
-        <v>724705</v>
+        <v>724605</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1146,7 +1146,7 @@
         <v>638</v>
       </c>
       <c r="J17">
-        <v>26615</v>
+        <v>26764</v>
       </c>
       <c r="K17">
         <v>13191</v>
@@ -1155,7 +1155,7 @@
         <v>314828</v>
       </c>
       <c r="M17">
-        <v>751320</v>
+        <v>751369</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -589,7 +589,7 @@
         <v>15</v>
       </c>
       <c r="B4">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -598,13 +598,13 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
       <c r="G4">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H4">
         <v>0</v>
@@ -616,7 +616,7 @@
         <v>11972</v>
       </c>
       <c r="K4">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="L4">
         <v>72479</v>
@@ -630,37 +630,37 @@
         <v>16</v>
       </c>
       <c r="B5">
-        <v>568</v>
+        <v>605</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>100</v>
+        <v>98.5</v>
       </c>
       <c r="E5">
-        <v>568</v>
+        <v>639</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G5">
-        <v>568</v>
+        <v>639</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="I5">
-        <v>6258</v>
+        <v>8081</v>
       </c>
       <c r="J5">
         <v>56244</v>
       </c>
       <c r="K5">
-        <v>1111</v>
+        <v>1149</v>
       </c>
       <c r="L5">
-        <v>78737</v>
+        <v>80560</v>
       </c>
       <c r="M5">
         <v>78308</v>
@@ -671,37 +671,37 @@
         <v>17</v>
       </c>
       <c r="B6">
-        <v>629</v>
+        <v>715</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="E6">
-        <v>629</v>
+        <v>739</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>629</v>
+        <v>739</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="I6">
-        <v>11071</v>
+        <v>11274</v>
       </c>
       <c r="J6">
         <v>49346</v>
       </c>
       <c r="K6">
-        <v>1740</v>
+        <v>1864</v>
       </c>
       <c r="L6">
-        <v>89808</v>
+        <v>91834</v>
       </c>
       <c r="M6">
         <v>127654</v>
@@ -712,40 +712,40 @@
         <v>18</v>
       </c>
       <c r="B7">
-        <v>429</v>
+        <v>491</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>99.8</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="E7">
-        <v>429</v>
+        <v>504</v>
       </c>
       <c r="F7">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="G7">
-        <v>429</v>
+        <v>504</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="I7">
-        <v>2171</v>
+        <v>2656</v>
       </c>
       <c r="J7">
-        <v>37862</v>
+        <v>38044</v>
       </c>
       <c r="K7">
-        <v>2169</v>
+        <v>2355</v>
       </c>
       <c r="L7">
-        <v>91979</v>
+        <v>94490</v>
       </c>
       <c r="M7">
-        <v>165516</v>
+        <v>165698</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -753,40 +753,40 @@
         <v>19</v>
       </c>
       <c r="B8">
-        <v>812</v>
+        <v>924</v>
       </c>
       <c r="C8">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D8">
-        <v>99</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="E8">
-        <v>819</v>
+        <v>940</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>892</v>
+        <v>1063</v>
       </c>
       <c r="H8">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="I8">
-        <v>11103</v>
+        <v>11143</v>
       </c>
       <c r="J8">
-        <v>10409</v>
+        <v>11398</v>
       </c>
       <c r="K8">
-        <v>2981</v>
+        <v>3279</v>
       </c>
       <c r="L8">
-        <v>103082</v>
+        <v>105633</v>
       </c>
       <c r="M8">
-        <v>175925</v>
+        <v>177096</v>
       </c>
     </row>
     <row r="9" spans="1:13">
@@ -794,40 +794,40 @@
         <v>20</v>
       </c>
       <c r="B9">
-        <v>821</v>
+        <v>997</v>
       </c>
       <c r="C9">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="D9">
-        <v>97.7</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="E9">
-        <v>856</v>
+        <v>1056</v>
       </c>
       <c r="F9">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="G9">
-        <v>1033</v>
+        <v>1479</v>
       </c>
       <c r="H9">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I9">
-        <v>12312</v>
+        <v>13560</v>
       </c>
       <c r="J9">
-        <v>32847</v>
+        <v>34803</v>
       </c>
       <c r="K9">
-        <v>3802</v>
+        <v>4276</v>
       </c>
       <c r="L9">
-        <v>115394</v>
+        <v>119193</v>
       </c>
       <c r="M9">
-        <v>208772</v>
+        <v>211899</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -835,40 +835,40 @@
         <v>21</v>
       </c>
       <c r="B10">
-        <v>1486</v>
+        <v>1500</v>
       </c>
       <c r="C10">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="D10">
-        <v>98.3</v>
+        <v>95.5</v>
       </c>
       <c r="E10">
-        <v>1501</v>
+        <v>1532</v>
       </c>
       <c r="F10">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="G10">
-        <v>1580</v>
+        <v>1700</v>
       </c>
       <c r="H10">
-        <v>30</v>
+        <v>79</v>
       </c>
       <c r="I10">
-        <v>73914</v>
+        <v>73816</v>
       </c>
       <c r="J10">
-        <v>62642</v>
+        <v>65377</v>
       </c>
       <c r="K10">
-        <v>5288</v>
+        <v>5776</v>
       </c>
       <c r="L10">
-        <v>189308</v>
+        <v>193009</v>
       </c>
       <c r="M10">
-        <v>271414</v>
+        <v>277276</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -876,40 +876,40 @@
         <v>22</v>
       </c>
       <c r="B11">
-        <v>876</v>
+        <v>840</v>
       </c>
       <c r="C11">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="D11">
-        <v>90.5</v>
+        <v>86.5</v>
       </c>
       <c r="E11">
-        <v>889</v>
+        <v>853</v>
       </c>
       <c r="F11">
-        <v>98</v>
+        <v>140</v>
       </c>
       <c r="G11">
-        <v>893</v>
+        <v>860</v>
       </c>
       <c r="H11">
-        <v>104</v>
+        <v>149</v>
       </c>
       <c r="I11">
-        <v>68334</v>
+        <v>67629</v>
       </c>
       <c r="J11">
-        <v>35898</v>
+        <v>39193</v>
       </c>
       <c r="K11">
-        <v>6164</v>
+        <v>6616</v>
       </c>
       <c r="L11">
-        <v>257642</v>
+        <v>260638</v>
       </c>
       <c r="M11">
-        <v>307312</v>
+        <v>316469</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -917,40 +917,40 @@
         <v>23</v>
       </c>
       <c r="B12">
-        <v>571</v>
+        <v>560</v>
       </c>
       <c r="C12">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="D12">
-        <v>59.3</v>
+        <v>58.2</v>
       </c>
       <c r="E12">
-        <v>672</v>
+        <v>660</v>
       </c>
       <c r="F12">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="G12">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="H12">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="I12">
         <v>12385</v>
       </c>
       <c r="J12">
-        <v>49429</v>
+        <v>49925</v>
       </c>
       <c r="K12">
-        <v>6735</v>
+        <v>7176</v>
       </c>
       <c r="L12">
-        <v>270027</v>
+        <v>273023</v>
       </c>
       <c r="M12">
-        <v>356741</v>
+        <v>366394</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -958,40 +958,40 @@
         <v>24</v>
       </c>
       <c r="B13">
-        <v>2975</v>
+        <v>2937</v>
       </c>
       <c r="C13">
-        <v>511</v>
+        <v>549</v>
       </c>
       <c r="D13">
-        <v>85.3</v>
+        <v>84.3</v>
       </c>
       <c r="E13">
-        <v>3095</v>
+        <v>3053</v>
       </c>
       <c r="F13">
-        <v>641</v>
+        <v>683</v>
       </c>
       <c r="G13">
-        <v>3126</v>
+        <v>3084</v>
       </c>
       <c r="H13">
-        <v>655</v>
+        <v>697</v>
       </c>
       <c r="I13">
-        <v>18261</v>
+        <v>17811</v>
       </c>
       <c r="J13">
-        <v>128117</v>
+        <v>130696</v>
       </c>
       <c r="K13">
-        <v>9710</v>
+        <v>10113</v>
       </c>
       <c r="L13">
-        <v>288288</v>
+        <v>290834</v>
       </c>
       <c r="M13">
-        <v>484858</v>
+        <v>497090</v>
       </c>
     </row>
     <row r="14" spans="1:13">
@@ -999,40 +999,40 @@
         <v>25</v>
       </c>
       <c r="B14">
-        <v>1760</v>
+        <v>1739</v>
       </c>
       <c r="C14">
-        <v>414</v>
+        <v>435</v>
       </c>
       <c r="D14">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E14">
-        <v>1837</v>
+        <v>1816</v>
       </c>
       <c r="F14">
-        <v>562</v>
+        <v>583</v>
       </c>
       <c r="G14">
-        <v>1853</v>
+        <v>1832</v>
       </c>
       <c r="H14">
-        <v>597</v>
+        <v>618</v>
       </c>
       <c r="I14">
-        <v>3025</v>
+        <v>3002</v>
       </c>
       <c r="J14">
-        <v>33334</v>
+        <v>35024</v>
       </c>
       <c r="K14">
-        <v>11470</v>
+        <v>11852</v>
       </c>
       <c r="L14">
-        <v>291313</v>
+        <v>293836</v>
       </c>
       <c r="M14">
-        <v>518192</v>
+        <v>532114</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1040,25 +1040,25 @@
         <v>26</v>
       </c>
       <c r="B15">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="C15">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="D15">
-        <v>39.7</v>
+        <v>38.8</v>
       </c>
       <c r="E15">
-        <v>788</v>
+        <v>770</v>
       </c>
       <c r="F15">
-        <v>1289</v>
+        <v>1307</v>
       </c>
       <c r="G15">
-        <v>939</v>
+        <v>918</v>
       </c>
       <c r="H15">
-        <v>1502</v>
+        <v>1523</v>
       </c>
       <c r="I15">
         <v>11817</v>
@@ -1067,13 +1067,13 @@
         <v>88451</v>
       </c>
       <c r="K15">
-        <v>11989</v>
+        <v>12359</v>
       </c>
       <c r="L15">
-        <v>303130</v>
+        <v>305653</v>
       </c>
       <c r="M15">
-        <v>606643</v>
+        <v>620565</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1081,25 +1081,25 @@
         <v>27</v>
       </c>
       <c r="B16">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C16">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D16">
-        <v>41.6</v>
+        <v>41.4</v>
       </c>
       <c r="E16">
         <v>409</v>
       </c>
       <c r="F16">
-        <v>629</v>
+        <v>635</v>
       </c>
       <c r="G16">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H16">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="I16">
         <v>11060</v>
@@ -1108,13 +1108,13 @@
         <v>117962</v>
       </c>
       <c r="K16">
-        <v>12320</v>
+        <v>12688</v>
       </c>
       <c r="L16">
-        <v>314190</v>
+        <v>316713</v>
       </c>
       <c r="M16">
-        <v>724605</v>
+        <v>738527</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1122,25 +1122,25 @@
         <v>28</v>
       </c>
       <c r="B17">
-        <v>871</v>
+        <v>854</v>
       </c>
       <c r="C17">
-        <v>946</v>
+        <v>964</v>
       </c>
       <c r="D17">
-        <v>47.9</v>
+        <v>47</v>
       </c>
       <c r="E17">
-        <v>1140</v>
+        <v>1115</v>
       </c>
       <c r="F17">
-        <v>1409</v>
+        <v>1437</v>
       </c>
       <c r="G17">
-        <v>1292</v>
+        <v>1265</v>
       </c>
       <c r="H17">
-        <v>1557</v>
+        <v>1588</v>
       </c>
       <c r="I17">
         <v>638</v>
@@ -1149,13 +1149,13 @@
         <v>26764</v>
       </c>
       <c r="K17">
-        <v>13191</v>
+        <v>13542</v>
       </c>
       <c r="L17">
-        <v>314828</v>
+        <v>317351</v>
       </c>
       <c r="M17">
-        <v>751369</v>
+        <v>765291</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1105,7 +1105,7 @@
         <v>11060</v>
       </c>
       <c r="J16">
-        <v>117962</v>
+        <v>117964</v>
       </c>
       <c r="K16">
         <v>12688</v>
@@ -1114,7 +1114,7 @@
         <v>316713</v>
       </c>
       <c r="M16">
-        <v>738527</v>
+        <v>738529</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1143,19 +1143,19 @@
         <v>1588</v>
       </c>
       <c r="I17">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="J17">
-        <v>26764</v>
+        <v>26772</v>
       </c>
       <c r="K17">
         <v>13542</v>
       </c>
       <c r="L17">
-        <v>317351</v>
+        <v>317352</v>
       </c>
       <c r="M17">
-        <v>765291</v>
+        <v>765301</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1,40 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>New_creators</t>
+  </si>
+  <si>
+    <t>Old_creators</t>
+  </si>
+  <si>
+    <t>New_share_pct</t>
+  </si>
+  <si>
+    <t>Sample_orders_new</t>
+  </si>
+  <si>
+    <t>Sample_orders_old</t>
+  </si>
+  <si>
+    <t>Sample_units_new</t>
+  </si>
+  <si>
+    <t>Sample_units_old</t>
+  </si>
+  <si>
+    <t>Video_GMV_new</t>
+  </si>
+  <si>
+    <t>Video_GMV_old</t>
+  </si>
+  <si>
+    <t>Cum_new_creators</t>
+  </si>
+  <si>
+    <t>Cum_GMV_new</t>
+  </si>
+  <si>
+    <t>Cum_GMV_old</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +140,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,770 +457,708 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>New_creators</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Old_creators</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>New_share_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Sample_orders_new</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Sample_orders_old</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Sample_units_new</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sample_units_old</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Video_GMV_new</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Video_GMV_old</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Cum_new_creators</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_new</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_old</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
         <v>70</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>70</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>70</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>2730</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>70</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>2730</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>41</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>41</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>41</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>6899</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>10092</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>111</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>9629</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>10092</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
         <v>433</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>433</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>434</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>62850</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>11972</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>544</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>72479</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>22064</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>605</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>9</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>98.5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>639</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>9</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>639</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>8081</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>56244</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1149</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>80560</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>78308</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>715</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>14</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>98.09999999999999</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>739</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>14</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>739</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>14</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>11274</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>49346</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>1864</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>91834</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>127654</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>491</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>21</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>95.90000000000001</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>504</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>21</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>504</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>21</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>2656</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>38044</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>2355</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>94490</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>165698</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>924</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>20</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>97.90000000000001</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>940</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>21</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>1063</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>32</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>11143</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>11398</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>3279</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>105633</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>177096</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>997</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>48</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>95.40000000000001</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>1056</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>50</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1479</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>67</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>13560</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>34803</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>4276</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>119193</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>211899</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>1500</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>70</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>95.5</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1532</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>74</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1700</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>79</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>73816</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>65377</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>5776</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>193009</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>277276</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
         <v>840</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>131</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>86.5</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>853</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>140</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>860</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>149</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>67629</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>39193</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6616</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>260638</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>316469</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
         <v>560</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>403</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>58.2</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>660</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>464</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>673</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>469</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>12385</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>49925</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>7176</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>273023</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>366394</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
         <v>2937</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>549</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>84.3</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3053</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>683</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>3084</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>697</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>17811</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>130696</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>10113</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>290834</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>497090</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
         <v>1739</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>435</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>80</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>1816</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>583</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>1832</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>618</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>3002</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>35024</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>11852</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>293836</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>532114</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
         <v>507</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>801</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>38.8</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>770</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1307</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>918</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1523</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>11817</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>88451</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>12359</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>305653</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>620565</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
         <v>329</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>466</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>41.4</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>409</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>635</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>456</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>704</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>11060</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>117964</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>12688</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>316713</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>738529</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
         <v>935</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>1023</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>47.8</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>1230</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>1537</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>1393</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>1689</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>639</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>26772</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>13623</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>317352</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>765301</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1,40 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>New_creators</t>
+  </si>
+  <si>
+    <t>Old_creators</t>
+  </si>
+  <si>
+    <t>New_share_pct</t>
+  </si>
+  <si>
+    <t>Sample_orders_new</t>
+  </si>
+  <si>
+    <t>Sample_orders_old</t>
+  </si>
+  <si>
+    <t>Sample_units_new</t>
+  </si>
+  <si>
+    <t>Sample_units_old</t>
+  </si>
+  <si>
+    <t>Video_GMV_new</t>
+  </si>
+  <si>
+    <t>Video_GMV_old</t>
+  </si>
+  <si>
+    <t>Cum_new_creators</t>
+  </si>
+  <si>
+    <t>Cum_GMV_new</t>
+  </si>
+  <si>
+    <t>Cum_GMV_old</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +140,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,770 +457,708 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>New_creators</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Old_creators</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>New_share_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Sample_orders_new</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Sample_orders_old</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Sample_units_new</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sample_units_old</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Video_GMV_new</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Video_GMV_old</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Cum_new_creators</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_new</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_old</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
         <v>70</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>70</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>70</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>2730</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>70</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>2730</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>41</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>41</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>41</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>6899</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>10092</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>111</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>9629</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>10092</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
         <v>433</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>433</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>434</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>62850</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>11972</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>544</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>72479</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>22064</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>605</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>9</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>98.5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>639</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>9</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>639</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>8081</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>56244</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1149</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>80560</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>78308</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>715</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>14</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>98.09999999999999</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>739</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>14</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>739</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>14</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>11274</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>49346</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>1864</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>91834</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>127654</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>491</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>21</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>95.90000000000001</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>504</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>21</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>504</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>21</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>2656</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>38044</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>2355</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>94490</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>165698</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>924</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>20</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>97.90000000000001</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>940</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>21</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>1063</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>32</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>11143</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>11398</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>3279</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>105633</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>177096</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>997</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>48</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>95.40000000000001</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>1056</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>50</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1479</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>67</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>13560</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>34803</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>4276</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>119193</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>211899</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>1500</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>70</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>95.5</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1532</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>74</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1700</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>79</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>73816</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>65377</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>5776</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>193009</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>277276</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
         <v>840</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>131</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>86.5</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>853</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>140</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>860</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>149</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>67629</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>39193</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6616</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>260638</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>316469</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
         <v>560</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>403</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>58.2</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>660</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>464</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>673</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>469</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>12385</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>49925</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>7176</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>273023</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>366394</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
         <v>2937</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>549</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>84.3</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3053</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>683</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>3084</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>697</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>17811</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>130696</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>10113</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>290834</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>497090</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
         <v>1739</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>435</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>80</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>1816</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>583</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>1832</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>618</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>3035</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>35229</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>11852</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>293869</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>532319</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
         <v>507</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>801</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>38.8</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>770</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1307</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>918</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1523</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>11506</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>86615</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>12359</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>305375</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>618934</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
         <v>329</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>466</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>41.4</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>409</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>635</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>456</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>704</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>11143</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>119918</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>12688</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>316518</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>738852</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>934</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1023</v>
-      </c>
-      <c r="D17" t="n">
-        <v>47.7</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1229</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1537</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1392</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1689</v>
-      </c>
-      <c r="I17" t="n">
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
+        <v>1112</v>
+      </c>
+      <c r="C17">
+        <v>1144</v>
+      </c>
+      <c r="D17">
+        <v>49.3</v>
+      </c>
+      <c r="E17">
+        <v>1446</v>
+      </c>
+      <c r="F17">
+        <v>1719</v>
+      </c>
+      <c r="G17">
+        <v>1612</v>
+      </c>
+      <c r="H17">
+        <v>1871</v>
+      </c>
+      <c r="I17">
         <v>921</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>29665</v>
       </c>
-      <c r="K17" t="n">
-        <v>13622</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K17">
+        <v>13800</v>
+      </c>
+      <c r="L17">
         <v>317439</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>768517</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1,40 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>New_creators</t>
+  </si>
+  <si>
+    <t>Old_creators</t>
+  </si>
+  <si>
+    <t>New_share_pct</t>
+  </si>
+  <si>
+    <t>Sample_orders_new</t>
+  </si>
+  <si>
+    <t>Sample_orders_old</t>
+  </si>
+  <si>
+    <t>Sample_units_new</t>
+  </si>
+  <si>
+    <t>Sample_units_old</t>
+  </si>
+  <si>
+    <t>Video_GMV_new</t>
+  </si>
+  <si>
+    <t>Video_GMV_old</t>
+  </si>
+  <si>
+    <t>Cum_new_creators</t>
+  </si>
+  <si>
+    <t>Cum_GMV_new</t>
+  </si>
+  <si>
+    <t>Cum_GMV_old</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +140,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,770 +457,708 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>New_creators</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Old_creators</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>New_share_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Sample_orders_new</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Sample_orders_old</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Sample_units_new</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sample_units_old</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Video_GMV_new</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Video_GMV_old</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Cum_new_creators</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_new</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_old</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
         <v>70</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>70</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>70</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>2730</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>70</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>2730</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>41</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>41</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>41</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>6899</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>10092</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>111</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>9629</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>10092</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
         <v>433</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>433</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>434</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>62850</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>11972</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>544</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>72479</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>22064</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>605</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>9</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>98.5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>639</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>9</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>639</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>8081</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>56244</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1149</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>80560</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>78308</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>715</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>14</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>98.09999999999999</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>739</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>14</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>739</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>14</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>11274</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>49346</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>1864</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>91834</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>127654</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>491</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>21</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>95.90000000000001</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>504</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>21</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>504</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>21</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>2656</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>38044</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>2355</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>94490</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>165698</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>924</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>20</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>97.90000000000001</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>940</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>21</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>1063</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>32</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>11143</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>11398</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>3279</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>105633</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>177096</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>997</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>48</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>95.40000000000001</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>1056</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>50</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1479</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>67</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>13560</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>34803</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>4276</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>119193</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>211899</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>1500</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>70</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>95.5</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1532</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>74</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1700</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>79</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>73816</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>65377</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>5776</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>193009</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>277276</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
         <v>840</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>131</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>86.5</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>853</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>140</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>860</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>149</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>67629</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>39193</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6616</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>260638</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>316469</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
         <v>560</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>403</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>58.2</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>660</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>464</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>673</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>469</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>12385</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>49925</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>7176</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>273023</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>366394</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
         <v>2937</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>549</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>84.3</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3053</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>683</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>3084</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>697</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>17811</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>130696</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>10113</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>290834</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>497090</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
         <v>1739</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>435</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>80</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>1816</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>583</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>1832</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>618</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>3035</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>35229</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>11852</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>293869</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>532319</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
         <v>507</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>801</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>38.8</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>770</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1307</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>918</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1523</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>11506</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>86615</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>12359</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>305375</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>618934</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
         <v>329</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>466</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>41.4</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>409</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>635</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>456</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>704</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>11143</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>119918</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>12688</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>316518</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>738852</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
         <v>1112</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>1144</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>49.3</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>1446</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>1719</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>1612</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>1871</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>921</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>29665</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>13800</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>317439</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>768517</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1020,19 +1020,19 @@
         <v>618</v>
       </c>
       <c r="I14">
-        <v>3035</v>
+        <v>3109</v>
       </c>
       <c r="J14">
-        <v>35229</v>
+        <v>35726</v>
       </c>
       <c r="K14">
         <v>11852</v>
       </c>
       <c r="L14">
-        <v>293869</v>
+        <v>293943</v>
       </c>
       <c r="M14">
-        <v>532319</v>
+        <v>532816</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1061,19 +1061,19 @@
         <v>1523</v>
       </c>
       <c r="I15">
-        <v>11506</v>
+        <v>10459</v>
       </c>
       <c r="J15">
-        <v>86615</v>
+        <v>77355</v>
       </c>
       <c r="K15">
         <v>12359</v>
       </c>
       <c r="L15">
-        <v>305375</v>
+        <v>304402</v>
       </c>
       <c r="M15">
-        <v>618934</v>
+        <v>610171</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1102,19 +1102,19 @@
         <v>704</v>
       </c>
       <c r="I16">
-        <v>11143</v>
+        <v>11239</v>
       </c>
       <c r="J16">
-        <v>119918</v>
+        <v>125839</v>
       </c>
       <c r="K16">
         <v>12688</v>
       </c>
       <c r="L16">
-        <v>316518</v>
+        <v>315641</v>
       </c>
       <c r="M16">
-        <v>738852</v>
+        <v>736010</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1143,19 +1143,19 @@
         <v>1871</v>
       </c>
       <c r="I17">
-        <v>921</v>
+        <v>1470</v>
       </c>
       <c r="J17">
-        <v>29665</v>
+        <v>35823</v>
       </c>
       <c r="K17">
         <v>13800</v>
       </c>
       <c r="L17">
-        <v>317439</v>
+        <v>317111</v>
       </c>
       <c r="M17">
-        <v>768517</v>
+        <v>771833</v>
       </c>
     </row>
   </sheetData>

--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1,40 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>New_creators</t>
+  </si>
+  <si>
+    <t>Old_creators</t>
+  </si>
+  <si>
+    <t>New_share_pct</t>
+  </si>
+  <si>
+    <t>Sample_orders_new</t>
+  </si>
+  <si>
+    <t>Sample_orders_old</t>
+  </si>
+  <si>
+    <t>Sample_units_new</t>
+  </si>
+  <si>
+    <t>Sample_units_old</t>
+  </si>
+  <si>
+    <t>Video_GMV_new</t>
+  </si>
+  <si>
+    <t>Video_GMV_old</t>
+  </si>
+  <si>
+    <t>Cum_new_creators</t>
+  </si>
+  <si>
+    <t>Cum_GMV_new</t>
+  </si>
+  <si>
+    <t>Cum_GMV_old</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +140,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,770 +457,708 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>New_creators</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Old_creators</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>New_share_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Sample_orders_new</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Sample_orders_old</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Sample_units_new</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sample_units_old</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Video_GMV_new</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Video_GMV_old</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Cum_new_creators</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_new</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_old</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
         <v>70</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>70</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>70</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>2730</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>70</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>2730</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>41</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>41</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>41</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>6899</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>10092</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>111</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>9629</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>10092</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
         <v>433</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>433</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>434</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>62850</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>11972</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>544</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>72479</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>22064</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>605</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>9</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>98.5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>639</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>9</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>639</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>8081</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>56244</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1149</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>80560</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>78308</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>715</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>14</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>98.09999999999999</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>739</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>14</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>739</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>14</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>11274</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>49346</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>1864</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>91834</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>127654</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>491</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>21</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>95.90000000000001</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>504</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>21</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>504</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>21</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>2656</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>38044</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>2355</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>94490</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>165698</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>924</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>20</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>97.90000000000001</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>940</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>21</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>1063</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>32</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>11143</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>11398</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>3279</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>105633</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>177096</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>997</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>48</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>95.40000000000001</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>1056</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>50</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1479</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>67</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>13560</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>34803</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>4276</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>119193</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>211899</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>1500</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>70</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>95.5</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1532</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>74</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1700</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>79</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>73816</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>65377</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>5776</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>193009</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>277276</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
         <v>840</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>131</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>86.5</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>853</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>140</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>860</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>149</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>67629</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>39193</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6616</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>260638</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>316469</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
         <v>560</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>403</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>58.2</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>660</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>464</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>673</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>469</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>12385</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>49925</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>7176</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>273023</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>366394</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
         <v>2937</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>549</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>84.3</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3053</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>683</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>3084</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>697</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>17811</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>130696</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>10113</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>290834</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>497090</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
         <v>1739</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>435</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>80</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>1816</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>583</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>1832</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>618</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>3109</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>35726</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>11852</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>293943</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>532816</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
         <v>507</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>801</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>38.8</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>770</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1307</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>918</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1523</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>10459</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>77355</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>12359</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>304402</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>610171</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
         <v>329</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>466</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>41.4</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>409</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>635</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>456</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>704</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>11239</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>125839</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>12688</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>315641</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>736010</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
         <v>1112</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>1144</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>49.3</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>1446</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>1719</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>1612</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>1871</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>1470</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>35823</v>
       </c>
-      <c r="K17" t="n">
+      <c r="K17">
         <v>13800</v>
       </c>
-      <c r="L17" t="n">
+      <c r="L17">
         <v>317111</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>771833</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1,40 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>New_creators</t>
+  </si>
+  <si>
+    <t>Old_creators</t>
+  </si>
+  <si>
+    <t>New_share_pct</t>
+  </si>
+  <si>
+    <t>Sample_orders_new</t>
+  </si>
+  <si>
+    <t>Sample_orders_old</t>
+  </si>
+  <si>
+    <t>Sample_units_new</t>
+  </si>
+  <si>
+    <t>Sample_units_old</t>
+  </si>
+  <si>
+    <t>Video_GMV_new</t>
+  </si>
+  <si>
+    <t>Video_GMV_old</t>
+  </si>
+  <si>
+    <t>Cum_new_creators</t>
+  </si>
+  <si>
+    <t>Cum_GMV_new</t>
+  </si>
+  <si>
+    <t>Cum_GMV_old</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +140,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,770 +457,708 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>New_creators</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Old_creators</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>New_share_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Sample_orders_new</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Sample_orders_old</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Sample_units_new</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sample_units_old</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Video_GMV_new</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Video_GMV_old</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Cum_new_creators</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_new</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_old</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
         <v>70</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>70</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>70</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>2730</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>70</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>2730</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>41</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>41</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>41</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>6899</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>10092</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>111</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>9629</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>10092</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
         <v>433</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>433</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>434</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>62850</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>11972</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>544</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>72479</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>22064</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>605</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>9</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>98.5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>639</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>9</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>639</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>8081</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>56244</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1149</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>80560</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>78308</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>715</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>14</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>98.09999999999999</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>739</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>14</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>739</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>14</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>11274</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>49346</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>1864</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>91834</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>127654</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>491</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>21</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>95.90000000000001</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>504</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>21</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>504</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>21</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>2656</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>38044</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>2355</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>94490</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>165698</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>924</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>20</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>97.90000000000001</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>940</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>21</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>1063</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>32</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>11143</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>11398</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>3279</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>105633</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>177096</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>997</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>48</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>95.40000000000001</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>1056</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>50</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1479</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>67</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>13560</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>34803</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>4276</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>119193</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>211899</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>1500</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>70</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>95.5</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1532</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>74</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1700</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>79</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>73816</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>65377</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>5776</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>193009</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>277276</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
         <v>840</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>131</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>86.5</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>853</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>140</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>860</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>149</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>67629</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>39193</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6616</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>260638</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>316469</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
         <v>560</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>403</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>58.2</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>660</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>464</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>673</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>469</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>12385</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>49925</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>7176</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>273023</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>366394</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
         <v>2937</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>549</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>84.3</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3053</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>683</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>3084</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>697</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>17811</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>130696</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>10113</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>290834</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>497090</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
         <v>1739</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>435</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>80</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>1816</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>583</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>1832</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>618</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>3109</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>35726</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>11852</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>293943</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>532816</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
         <v>507</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>801</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>38.8</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>770</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1307</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>918</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1523</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>10459</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>77355</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>12359</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>304402</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>610171</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
         <v>329</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>466</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>41.4</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>409</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>635</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>456</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>704</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>11239</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>125839</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>12688</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>315641</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>736010</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1164</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1174</v>
-      </c>
-      <c r="D17" t="n">
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
+        <v>1162</v>
+      </c>
+      <c r="C17">
+        <v>1172</v>
+      </c>
+      <c r="D17">
         <v>49.8</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>1523</v>
       </c>
-      <c r="F17" t="n">
-        <v>1780</v>
-      </c>
-      <c r="G17" t="n">
+      <c r="F17">
+        <v>1777</v>
+      </c>
+      <c r="G17">
         <v>1689</v>
       </c>
-      <c r="H17" t="n">
-        <v>1932</v>
-      </c>
-      <c r="I17" t="n">
+      <c r="H17">
+        <v>1929</v>
+      </c>
+      <c r="I17">
         <v>1470</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>35823</v>
       </c>
-      <c r="K17" t="n">
-        <v>13852</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K17">
+        <v>13850</v>
+      </c>
+      <c r="L17">
         <v>317111</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>771833</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1,40 +1,138 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+  <si>
+    <t>Month</t>
+  </si>
+  <si>
+    <t>New_creators</t>
+  </si>
+  <si>
+    <t>Old_creators</t>
+  </si>
+  <si>
+    <t>New_share_pct</t>
+  </si>
+  <si>
+    <t>Sample_orders_new</t>
+  </si>
+  <si>
+    <t>Sample_orders_old</t>
+  </si>
+  <si>
+    <t>Sample_units_new</t>
+  </si>
+  <si>
+    <t>Sample_units_old</t>
+  </si>
+  <si>
+    <t>Video_GMV_new</t>
+  </si>
+  <si>
+    <t>Video_GMV_old</t>
+  </si>
+  <si>
+    <t>Cum_new_creators</t>
+  </si>
+  <si>
+    <t>Cum_GMV_new</t>
+  </si>
+  <si>
+    <t>Cum_GMV_old</t>
+  </si>
+  <si>
+    <t>2025-07</t>
+  </si>
+  <si>
+    <t>2025-08</t>
+  </si>
+  <si>
+    <t>2025-09</t>
+  </si>
+  <si>
+    <t>2025-10</t>
+  </si>
+  <si>
+    <t>2025-11</t>
+  </si>
+  <si>
+    <t>2025-12</t>
+  </si>
+  <si>
+    <t>2026-01</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>2026-03</t>
+  </si>
+  <si>
+    <t>2026-04</t>
+  </si>
+  <si>
+    <t>2026-05</t>
+  </si>
+  <si>
+    <t>2026-06</t>
+  </si>
+  <si>
+    <t>2026-07</t>
+  </si>
+  <si>
+    <t>2026-08</t>
+  </si>
+  <si>
+    <t>2026-09</t>
+  </si>
+  <si>
+    <t>2026-10</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +140,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,770 +457,708 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>New_creators</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Old_creators</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>New_share_pct</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Sample_orders_new</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Sample_orders_old</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Sample_units_new</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Sample_units_old</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Video_GMV_new</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Video_GMV_old</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Cum_new_creators</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_new</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Cum_GMV_old</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:13">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2">
         <v>70</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>100</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>70</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>70</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>2730</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>0</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>70</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>2730</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:13">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3">
         <v>41</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>100</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>41</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>41</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>0</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>6899</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>10092</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>111</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>9629</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>10092</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:13">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4">
         <v>433</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>100</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>433</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>434</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>62850</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>11972</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>544</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>72479</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>22064</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
         <v>605</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>9</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>98.5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>639</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>9</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>639</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>9</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>8081</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>56244</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1149</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>80560</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>78308</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
         <v>715</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>14</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>98.09999999999999</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>739</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>14</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>739</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>14</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>11274</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>49346</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>1864</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>91834</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>127654</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7">
         <v>491</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>21</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>95.90000000000001</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>504</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>21</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>504</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>21</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>2656</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7">
         <v>38044</v>
       </c>
-      <c r="K7" t="n">
+      <c r="K7">
         <v>2355</v>
       </c>
-      <c r="L7" t="n">
+      <c r="L7">
         <v>94490</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7">
         <v>165698</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8">
         <v>924</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>20</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>97.90000000000001</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8">
         <v>940</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>21</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>1063</v>
       </c>
-      <c r="H8" t="n">
+      <c r="H8">
         <v>32</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>11143</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8">
         <v>11398</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>3279</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L8">
         <v>105633</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M8">
         <v>177096</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
         <v>997</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>48</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>95.40000000000001</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>1056</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9">
         <v>50</v>
       </c>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>1479</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9">
         <v>67</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>13560</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9">
         <v>34803</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9">
         <v>4276</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L9">
         <v>119193</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M9">
         <v>211899</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10">
         <v>1500</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>70</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>95.5</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10">
         <v>1532</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10">
         <v>74</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>1700</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H10">
         <v>79</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>73816</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10">
         <v>65377</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>5776</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L10">
         <v>193009</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M10">
         <v>277276</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
         <v>840</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>131</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>86.5</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11">
         <v>853</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>140</v>
       </c>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>860</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>149</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>67629</v>
       </c>
-      <c r="J11" t="n">
+      <c r="J11">
         <v>39193</v>
       </c>
-      <c r="K11" t="n">
+      <c r="K11">
         <v>6616</v>
       </c>
-      <c r="L11" t="n">
+      <c r="L11">
         <v>260638</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M11">
         <v>316469</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
+    <row r="12" spans="1:13">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
         <v>560</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>403</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>58.2</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>660</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>464</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>673</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>469</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>12385</v>
       </c>
-      <c r="J12" t="n">
+      <c r="J12">
         <v>49925</v>
       </c>
-      <c r="K12" t="n">
+      <c r="K12">
         <v>7176</v>
       </c>
-      <c r="L12" t="n">
+      <c r="L12">
         <v>273023</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M12">
         <v>366394</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
         <v>2937</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>549</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>84.3</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>3053</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>683</v>
       </c>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>3084</v>
       </c>
-      <c r="H13" t="n">
+      <c r="H13">
         <v>697</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>17811</v>
       </c>
-      <c r="J13" t="n">
+      <c r="J13">
         <v>130696</v>
       </c>
-      <c r="K13" t="n">
+      <c r="K13">
         <v>10113</v>
       </c>
-      <c r="L13" t="n">
+      <c r="L13">
         <v>290834</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M13">
         <v>497090</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14">
         <v>1739</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>435</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>80</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14">
         <v>1816</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F14">
         <v>583</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>1832</v>
       </c>
-      <c r="H14" t="n">
+      <c r="H14">
         <v>618</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>3109</v>
       </c>
-      <c r="J14" t="n">
+      <c r="J14">
         <v>35736</v>
       </c>
-      <c r="K14" t="n">
+      <c r="K14">
         <v>11852</v>
       </c>
-      <c r="L14" t="n">
+      <c r="L14">
         <v>293943</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M14">
         <v>532826</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15">
         <v>507</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>801</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>38.8</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>770</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>1307</v>
       </c>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>918</v>
       </c>
-      <c r="H15" t="n">
+      <c r="H15">
         <v>1523</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>9789</v>
       </c>
-      <c r="J15" t="n">
+      <c r="J15">
         <v>72650</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>12359</v>
       </c>
-      <c r="L15" t="n">
+      <c r="L15">
         <v>303732</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M15">
         <v>605476</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
+    <row r="16" spans="1:13">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16">
         <v>329</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>466</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>41.4</v>
       </c>
-      <c r="E16" t="n">
+      <c r="E16">
         <v>409</v>
       </c>
-      <c r="F16" t="n">
+      <c r="F16">
         <v>635</v>
       </c>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>456</v>
       </c>
-      <c r="H16" t="n">
+      <c r="H16">
         <v>704</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>11410</v>
       </c>
-      <c r="J16" t="n">
+      <c r="J16">
         <v>129020</v>
       </c>
-      <c r="K16" t="n">
+      <c r="K16">
         <v>12688</v>
       </c>
-      <c r="L16" t="n">
+      <c r="L16">
         <v>315142</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M16">
         <v>734496</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1162</v>
-      </c>
-      <c r="C17" t="n">
-        <v>1172</v>
-      </c>
-      <c r="D17" t="n">
-        <v>49.8</v>
-      </c>
-      <c r="E17" t="n">
-        <v>1523</v>
-      </c>
-      <c r="F17" t="n">
-        <v>1777</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1689</v>
-      </c>
-      <c r="H17" t="n">
-        <v>1929</v>
-      </c>
-      <c r="I17" t="n">
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17">
+        <v>1198</v>
+      </c>
+      <c r="C17">
+        <v>1201</v>
+      </c>
+      <c r="D17">
+        <v>49.9</v>
+      </c>
+      <c r="E17">
+        <v>1572</v>
+      </c>
+      <c r="F17">
+        <v>1822</v>
+      </c>
+      <c r="G17">
+        <v>1738</v>
+      </c>
+      <c r="H17">
+        <v>1974</v>
+      </c>
+      <c r="I17">
         <v>1931</v>
       </c>
-      <c r="J17" t="n">
+      <c r="J17">
         <v>38422</v>
       </c>
-      <c r="K17" t="n">
-        <v>13850</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K17">
+        <v>13886</v>
+      </c>
+      <c r="L17">
         <v>317073</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M17">
         <v>772918</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/segment_monthly.xlsx
+++ b/segment_monthly.xlsx
@@ -1023,7 +1023,7 @@
         <v>3109</v>
       </c>
       <c r="J14">
-        <v>35736</v>
+        <v>35818</v>
       </c>
       <c r="K14">
         <v>11852</v>
@@ -1032,7 +1032,7 @@
         <v>293943</v>
       </c>
       <c r="M14">
-        <v>532826</v>
+        <v>532908</v>
       </c>
     </row>
     <row r="15" spans="1:13">
@@ -1061,19 +1061,19 @@
         <v>1523</v>
       </c>
       <c r="I15">
-        <v>9789</v>
+        <v>9348</v>
       </c>
       <c r="J15">
-        <v>72650</v>
+        <v>67419</v>
       </c>
       <c r="K15">
         <v>12359</v>
       </c>
       <c r="L15">
-        <v>303732</v>
+        <v>303291</v>
       </c>
       <c r="M15">
-        <v>605476</v>
+        <v>600327</v>
       </c>
     </row>
     <row r="16" spans="1:13">
@@ -1102,19 +1102,19 @@
         <v>704</v>
       </c>
       <c r="I16">
-        <v>11410</v>
+        <v>11526</v>
       </c>
       <c r="J16">
-        <v>129020</v>
+        <v>133379</v>
       </c>
       <c r="K16">
         <v>12688</v>
       </c>
       <c r="L16">
-        <v>315142</v>
+        <v>314817</v>
       </c>
       <c r="M16">
-        <v>734496</v>
+        <v>733706</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -1122,40 +1122,40 @@
         <v>28</v>
       </c>
       <c r="B17">
-        <v>1198</v>
+        <v>1307</v>
       </c>
       <c r="C17">
-        <v>1201</v>
+        <v>1267</v>
       </c>
       <c r="D17">
-        <v>49.9</v>
+        <v>50.8</v>
       </c>
       <c r="E17">
-        <v>1572</v>
+        <v>1714</v>
       </c>
       <c r="F17">
-        <v>1822</v>
+        <v>1925</v>
       </c>
       <c r="G17">
-        <v>1738</v>
+        <v>1885</v>
       </c>
       <c r="H17">
-        <v>1974</v>
+        <v>2078</v>
       </c>
       <c r="I17">
-        <v>1931</v>
+        <v>2253</v>
       </c>
       <c r="J17">
-        <v>38422</v>
+        <v>41404</v>
       </c>
       <c r="K17">
-        <v>13886</v>
+        <v>13995</v>
       </c>
       <c r="L17">
-        <v>317073</v>
+        <v>317070</v>
       </c>
       <c r="M17">
-        <v>772918</v>
+        <v>775110</v>
       </c>
     </row>
   </sheetData>
